--- a/21130317_Testplan.xlsx
+++ b/21130317_Testplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\For NLU\Final\tester2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF625FA-ACD4-4FF3-B2A7-A83A9F817B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13076436-7904-4CBC-92FD-A0942455598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34125" yWindow="1830" windowWidth="21600" windowHeight="11775" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="207">
   <si>
     <t>TEST PLAN</t>
   </si>
@@ -597,13 +597,7 @@
     <t>Test techniques</t>
   </si>
   <si>
-    <t>White box testing</t>
-  </si>
-  <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>Black box testing</t>
   </si>
   <si>
     <t>Developer</t>
@@ -936,6 +930,21 @@
   </si>
   <si>
     <t>Final version</t>
+  </si>
+  <si>
+    <t>Test report must be written by excel match with template.</t>
+  </si>
+  <si>
+    <t>Test case must cover requirement.</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>Functional Test</t>
+  </si>
+  <si>
+    <t>User Interface Test</t>
   </si>
 </sst>
 </file>
@@ -2934,7 +2943,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="325">
+  <cellXfs count="324">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3061,9 +3070,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3259,9 +3265,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3462,8 +3465,108 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="126" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="43" fillId="0" borderId="125" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3476,27 +3579,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3525,38 +3607,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3597,19 +3655,91 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3625,21 +3755,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3662,84 +3777,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3768,7 +3805,46 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3776,6 +3852,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3795,63 +3886,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="122" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="126" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3860,41 +3898,11 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="43" fillId="0" borderId="125" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4438,7 +4446,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="152400" y="1693545"/>
+          <a:off x="161925" y="1714500"/>
           <a:ext cx="2486025" cy="342900"/>
           <a:chOff x="4102988" y="3608550"/>
           <a:chExt cx="2486025" cy="342900"/>
@@ -4779,14 +4787,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="27.5" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="26" width="8" customWidth="1"/>
@@ -4823,13 +4831,13 @@
     <row r="2" spans="1:26" ht="72" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="200" t="s">
+      <c r="C2" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="202"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="198"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -4852,12 +4860,12 @@
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="203"/>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="205"/>
+      <c r="B3" s="199"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="201"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -4883,16 +4891,16 @@
       <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="202" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="185"/>
-      <c r="E4" s="186"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="204"/>
       <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -4919,15 +4927,15 @@
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="207" t="s">
+      <c r="C5" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="189"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="316">
+      <c r="G5" s="187">
         <v>45597</v>
       </c>
       <c r="H5" s="1"/>
@@ -4956,15 +4964,15 @@
         <v>7</v>
       </c>
       <c r="C6" s="208" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D6" s="209"/>
       <c r="E6" s="210"/>
       <c r="F6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="324" t="s">
-        <v>169</v>
+      <c r="G6" s="195" t="s">
+        <v>167</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -4991,11 +4999,11 @@
       <c r="B7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="190" t="s">
+      <c r="C7" s="211" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="180"/>
-      <c r="E7" s="181"/>
+      <c r="D7" s="212"/>
+      <c r="E7" s="213"/>
       <c r="F7" s="13" t="s">
         <v>11</v>
       </c>
@@ -5052,10 +5060,10 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="182" t="s">
+      <c r="B9" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="183"/>
+      <c r="C9" s="215"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -5082,7 +5090,7 @@
     </row>
     <row r="10" spans="1:26" ht="18" customHeight="1">
       <c r="A10" s="5"/>
-      <c r="B10" s="290" t="s">
+      <c r="B10" s="177" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="14" t="s">
@@ -5094,10 +5102,10 @@
       <c r="E10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="192" t="s">
+      <c r="F10" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="193"/>
+      <c r="G10" s="218"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -5120,20 +5128,20 @@
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
       <c r="A11" s="15"/>
-      <c r="B11" s="291">
+      <c r="B11" s="178">
         <v>45596</v>
       </c>
-      <c r="C11" s="319" t="s">
-        <v>201</v>
+      <c r="C11" s="190" t="s">
+        <v>199</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
-      <c r="F11" s="194"/>
-      <c r="G11" s="195"/>
+      <c r="F11" s="219"/>
+      <c r="G11" s="220"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -5156,20 +5164,20 @@
     </row>
     <row r="12" spans="1:26" ht="13.5" customHeight="1" thickBot="1">
       <c r="A12" s="15"/>
-      <c r="B12" s="323">
+      <c r="B12" s="194">
         <v>41944</v>
       </c>
-      <c r="C12" s="320" t="s">
+      <c r="C12" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="322" t="s">
-        <v>203</v>
+      <c r="D12" s="193" t="s">
+        <v>201</v>
       </c>
-      <c r="E12" s="321" t="s">
-        <v>202</v>
+      <c r="E12" s="192" t="s">
+        <v>200</v>
       </c>
-      <c r="F12" s="196"/>
-      <c r="G12" s="197"/>
+      <c r="F12" s="221"/>
+      <c r="G12" s="222"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -5220,10 +5228,10 @@
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="182" t="s">
+      <c r="B14" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="183"/>
+      <c r="C14" s="215"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -5253,12 +5261,12 @@
       <c r="B15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="198" t="s">
+      <c r="C15" s="223" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="185"/>
-      <c r="E15" s="185"/>
-      <c r="F15" s="186"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="204"/>
       <c r="G15" s="20" t="s">
         <v>21</v>
       </c>
@@ -5287,12 +5295,12 @@
       <c r="B16" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="199" t="s">
+      <c r="C16" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="188"/>
-      <c r="E16" s="188"/>
-      <c r="F16" s="189"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="207"/>
       <c r="G16" s="22"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5319,12 +5327,12 @@
       <c r="B17" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="191" t="s">
+      <c r="C17" s="216" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="188"/>
-      <c r="E17" s="188"/>
-      <c r="F17" s="189"/>
+      <c r="D17" s="206"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="207"/>
       <c r="G17" s="22"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5351,12 +5359,12 @@
       <c r="B18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="191" t="s">
+      <c r="C18" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="188"/>
-      <c r="E18" s="188"/>
-      <c r="F18" s="189"/>
+      <c r="D18" s="206"/>
+      <c r="E18" s="206"/>
+      <c r="F18" s="207"/>
       <c r="G18" s="22"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5383,12 +5391,12 @@
       <c r="B19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="191" t="s">
+      <c r="C19" s="216" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="188"/>
-      <c r="E19" s="188"/>
-      <c r="F19" s="189"/>
+      <c r="D19" s="206"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="207"/>
       <c r="G19" s="22"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5415,12 +5423,12 @@
       <c r="B20" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="191" t="s">
+      <c r="C20" s="216" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="188"/>
-      <c r="E20" s="188"/>
-      <c r="F20" s="189"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="207"/>
       <c r="G20" s="22"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5447,12 +5455,12 @@
       <c r="B21" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="179" t="s">
+      <c r="C21" s="225" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="180"/>
-      <c r="E21" s="180"/>
-      <c r="F21" s="181"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="213"/>
       <c r="G21" s="25" t="s">
         <v>34</v>
       </c>
@@ -5506,10 +5514,10 @@
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1">
       <c r="A23" s="26"/>
-      <c r="B23" s="182" t="s">
+      <c r="B23" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="183"/>
+      <c r="C23" s="215"/>
       <c r="D23" s="27"/>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -5536,12 +5544,12 @@
     </row>
     <row r="24" spans="1:26" ht="18" customHeight="1">
       <c r="A24" s="5"/>
-      <c r="B24" s="184" t="s">
+      <c r="B24" s="226" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="185"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="186"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="204"/>
       <c r="F24" s="14" t="s">
         <v>9</v>
       </c>
@@ -5570,12 +5578,12 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="15"/>
-      <c r="B25" s="187" t="s">
-        <v>173</v>
+      <c r="B25" s="227" t="s">
+        <v>171</v>
       </c>
-      <c r="C25" s="188"/>
-      <c r="D25" s="188"/>
-      <c r="E25" s="189"/>
+      <c r="C25" s="206"/>
+      <c r="D25" s="206"/>
+      <c r="E25" s="207"/>
       <c r="F25" s="30" t="s">
         <v>10</v>
       </c>
@@ -5602,10 +5610,10 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="15"/>
-      <c r="B26" s="187"/>
-      <c r="C26" s="188"/>
-      <c r="D26" s="188"/>
-      <c r="E26" s="189"/>
+      <c r="B26" s="227"/>
+      <c r="C26" s="206"/>
+      <c r="D26" s="206"/>
+      <c r="E26" s="207"/>
       <c r="F26" s="31"/>
       <c r="G26" s="22"/>
       <c r="H26" s="15"/>
@@ -11977,11 +11985,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="C18:F18"/>
@@ -11994,11 +12002,11 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -12014,15 +12022,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="57.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="60.85546875" customWidth="1"/>
+    <col min="3" max="3" width="57.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" customWidth="1"/>
     <col min="8" max="25" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12054,13 +12062,13 @@
       <c r="Y1" s="32"/>
     </row>
     <row r="2" spans="1:25" ht="26.25" customHeight="1">
-      <c r="A2" s="217" t="s">
+      <c r="A2" s="234" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
+      <c r="B2" s="235"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
       <c r="F2" s="34"/>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
@@ -12083,11 +12091,11 @@
       <c r="Y2" s="32"/>
     </row>
     <row r="3" spans="1:25" ht="13.5" customHeight="1">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
+      <c r="A3" s="235"/>
+      <c r="B3" s="235"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
       <c r="F3" s="33"/>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -12207,9 +12215,13 @@
       <c r="B7" s="43">
         <v>1</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="46"/>
+      <c r="C7" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="322" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="45"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
@@ -12233,12 +12245,16 @@
     </row>
     <row r="8" spans="1:25" ht="12.75" customHeight="1">
       <c r="A8" s="32"/>
-      <c r="B8" s="47">
+      <c r="B8" s="46">
         <v>2</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50"/>
+      <c r="C8" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="49"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
@@ -12380,11 +12396,11 @@
       <c r="C13" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="219" t="s">
+      <c r="D13" s="236" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="193"/>
-      <c r="F13" s="51"/>
+      <c r="E13" s="218"/>
+      <c r="F13" s="50"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
@@ -12410,10 +12426,10 @@
       <c r="B14" s="43">
         <v>1</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="238"/>
+      <c r="F14" s="50"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
@@ -12436,13 +12452,13 @@
     </row>
     <row r="15" spans="1:25" ht="13.5" customHeight="1">
       <c r="A15" s="32"/>
-      <c r="B15" s="54">
+      <c r="B15" s="53">
         <v>2</v>
       </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="51"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="239"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="50"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
@@ -12465,11 +12481,11 @@
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1">
       <c r="A16" s="32"/>
-      <c r="B16" s="57"/>
+      <c r="B16" s="56"/>
       <c r="C16" s="32"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="51"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="50"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
@@ -12556,13 +12572,13 @@
       <c r="C19" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="60" t="s">
+      <c r="E19" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="51"/>
+      <c r="F19" s="50"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
       <c r="I19" s="32"/>
@@ -12585,10 +12601,10 @@
     </row>
     <row r="20" spans="1:25" ht="13.5" customHeight="1">
       <c r="A20" s="32"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="64"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="63"/>
       <c r="F20" s="33"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
@@ -12612,10 +12628,10 @@
     </row>
     <row r="21" spans="1:25" ht="13.5" customHeight="1">
       <c r="A21" s="32"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="67"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="66"/>
       <c r="F21" s="33"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
@@ -12759,14 +12775,14 @@
     </row>
     <row r="26" spans="1:25" ht="33.75" customHeight="1">
       <c r="A26" s="32"/>
-      <c r="B26" s="68">
+      <c r="B26" s="67">
         <v>1</v>
       </c>
-      <c r="C26" s="69" t="s">
-        <v>171</v>
+      <c r="C26" s="68" t="s">
+        <v>169</v>
       </c>
-      <c r="D26" s="70"/>
-      <c r="E26" s="71" t="s">
+      <c r="D26" s="69"/>
+      <c r="E26" s="70" t="s">
         <v>51</v>
       </c>
       <c r="F26" s="32"/>
@@ -12792,14 +12808,14 @@
     </row>
     <row r="27" spans="1:25" ht="12.75" customHeight="1">
       <c r="A27" s="32"/>
-      <c r="B27" s="72">
+      <c r="B27" s="71">
         <v>2</v>
       </c>
-      <c r="C27" s="73" t="s">
+      <c r="C27" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="70"/>
-      <c r="E27" s="73"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="72"/>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
@@ -12823,14 +12839,14 @@
     </row>
     <row r="28" spans="1:25" ht="21.75" customHeight="1">
       <c r="A28" s="32"/>
-      <c r="B28" s="74">
+      <c r="B28" s="73">
         <v>3</v>
       </c>
-      <c r="C28" s="67" t="s">
+      <c r="C28" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="72"/>
-      <c r="E28" s="67"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="66"/>
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
       <c r="H28" s="32"/>
@@ -12945,10 +12961,10 @@
       <c r="C32" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="219" t="s">
+      <c r="D32" s="236" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="193"/>
+      <c r="E32" s="218"/>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
@@ -12972,14 +12988,14 @@
     </row>
     <row r="33" spans="1:25" ht="33" customHeight="1">
       <c r="A33" s="33"/>
-      <c r="B33" s="75">
+      <c r="B33" s="74">
         <v>1</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="222"/>
-      <c r="E33" s="223"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="240"/>
       <c r="F33" s="33"/>
       <c r="G33" s="33"/>
       <c r="H33" s="33"/>
@@ -13003,14 +13019,14 @@
     </row>
     <row r="34" spans="1:25" ht="31.5" customHeight="1">
       <c r="A34" s="33"/>
-      <c r="B34" s="75">
+      <c r="B34" s="74">
         <v>2</v>
       </c>
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="211"/>
-      <c r="E34" s="212"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="229"/>
       <c r="F34" s="33"/>
       <c r="G34" s="33"/>
       <c r="H34" s="33"/>
@@ -13034,14 +13050,14 @@
     </row>
     <row r="35" spans="1:25" ht="54" customHeight="1">
       <c r="A35" s="33"/>
-      <c r="B35" s="75">
+      <c r="B35" s="74">
         <v>3</v>
       </c>
-      <c r="C35" s="69" t="s">
+      <c r="C35" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="211"/>
-      <c r="E35" s="212"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="229"/>
       <c r="F35" s="33"/>
       <c r="G35" s="33"/>
       <c r="H35" s="33"/>
@@ -13063,16 +13079,16 @@
       <c r="X35" s="33"/>
       <c r="Y35" s="33"/>
     </row>
-    <row r="36" spans="1:25" ht="50.4" customHeight="1">
+    <row r="36" spans="1:25" ht="50.45" customHeight="1">
       <c r="A36" s="33"/>
-      <c r="B36" s="75">
+      <c r="B36" s="74">
         <v>4</v>
       </c>
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="213"/>
-      <c r="E36" s="214"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="231"/>
       <c r="F36" s="33"/>
       <c r="G36" s="33"/>
       <c r="H36" s="33"/>
@@ -13096,16 +13112,16 @@
     </row>
     <row r="37" spans="1:25" ht="15" customHeight="1">
       <c r="A37" s="32"/>
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="215" t="s">
+      <c r="D37" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="195"/>
+      <c r="E37" s="220"/>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
@@ -13129,14 +13145,14 @@
     </row>
     <row r="38" spans="1:25" ht="39.6" customHeight="1">
       <c r="A38" s="33"/>
-      <c r="B38" s="78">
+      <c r="B38" s="77">
         <v>1</v>
       </c>
-      <c r="C38" s="69" t="s">
+      <c r="C38" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="216"/>
-      <c r="E38" s="214"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="231"/>
       <c r="F38" s="33"/>
       <c r="G38" s="33"/>
       <c r="H38" s="33"/>
@@ -19345,16 +19361,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.85546875" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.140625" customWidth="1"/>
-    <col min="7" max="7" width="26.85546875" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.5" customWidth="1"/>
+    <col min="6" max="6" width="29.1640625" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" customWidth="1"/>
     <col min="9" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19389,9 +19405,9 @@
     <row r="2" spans="1:26" ht="32.25" customHeight="1">
       <c r="A2" s="32"/>
       <c r="B2" s="34"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="34"/>
@@ -19475,7 +19491,7 @@
       <c r="Z4" s="32"/>
     </row>
     <row r="5" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="79" t="s">
         <v>64</v>
       </c>
       <c r="B5" s="32"/>
@@ -19505,24 +19521,24 @@
       <c r="Z5" s="32"/>
     </row>
     <row r="6" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="226" t="s">
+      <c r="B6" s="258" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="246"/>
-      <c r="D6" s="234" t="s">
+      <c r="C6" s="259"/>
+      <c r="D6" s="253" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="246"/>
-      <c r="F6" s="82" t="s">
+      <c r="E6" s="259"/>
+      <c r="F6" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="234" t="s">
+      <c r="G6" s="253" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="228"/>
+      <c r="H6" s="254"/>
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
       <c r="K6" s="32"/>
@@ -19543,20 +19559,20 @@
       <c r="Z6" s="32"/>
     </row>
     <row r="7" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A7" s="83">
+      <c r="A7" s="82">
         <v>1</v>
       </c>
-      <c r="B7" s="249" t="s">
+      <c r="B7" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="236"/>
-      <c r="D7" s="249"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="84" t="s">
+      <c r="C7" s="243"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="253"/>
-      <c r="H7" s="254"/>
+      <c r="G7" s="262"/>
+      <c r="H7" s="245"/>
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
       <c r="K7" s="32"/>
@@ -19577,20 +19593,20 @@
       <c r="Z7" s="32"/>
     </row>
     <row r="8" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A8" s="83">
+      <c r="A8" s="82">
         <v>2</v>
       </c>
-      <c r="B8" s="249" t="s">
+      <c r="B8" s="255" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="236"/>
-      <c r="D8" s="250"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="84" t="s">
+      <c r="C8" s="243"/>
+      <c r="D8" s="256"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="250"/>
-      <c r="H8" s="254"/>
+      <c r="G8" s="256"/>
+      <c r="H8" s="245"/>
       <c r="I8" s="32"/>
       <c r="J8" s="32"/>
       <c r="K8" s="32"/>
@@ -19611,20 +19627,20 @@
       <c r="Z8" s="32"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="83">
+      <c r="A9" s="82">
         <v>3</v>
       </c>
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="257" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="236"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="84" t="s">
+      <c r="C9" s="243"/>
+      <c r="D9" s="256"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="250"/>
-      <c r="H9" s="254"/>
+      <c r="G9" s="256"/>
+      <c r="H9" s="245"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
@@ -19645,20 +19661,20 @@
       <c r="Z9" s="32"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="83">
+      <c r="A10" s="82">
         <v>4</v>
       </c>
-      <c r="B10" s="247" t="s">
+      <c r="B10" s="257" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="236"/>
-      <c r="D10" s="250"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="84" t="s">
+      <c r="C10" s="243"/>
+      <c r="D10" s="256"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="250"/>
-      <c r="H10" s="254"/>
+      <c r="G10" s="256"/>
+      <c r="H10" s="245"/>
       <c r="I10" s="32"/>
       <c r="J10" s="32"/>
       <c r="K10" s="32"/>
@@ -19679,20 +19695,20 @@
       <c r="Z10" s="32"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="83">
+      <c r="A11" s="82">
         <v>5</v>
       </c>
-      <c r="B11" s="249" t="s">
+      <c r="B11" s="255" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="236"/>
-      <c r="D11" s="250"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="84" t="s">
+      <c r="C11" s="243"/>
+      <c r="D11" s="256"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="250"/>
-      <c r="H11" s="254"/>
+      <c r="G11" s="256"/>
+      <c r="H11" s="245"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
       <c r="K11" s="32"/>
@@ -19713,20 +19729,20 @@
       <c r="Z11" s="32"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="83">
+      <c r="A12" s="82">
         <v>6</v>
       </c>
-      <c r="B12" s="249" t="s">
+      <c r="B12" s="255" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="236"/>
-      <c r="D12" s="250"/>
-      <c r="E12" s="236"/>
-      <c r="F12" s="84" t="s">
+      <c r="C12" s="243"/>
+      <c r="D12" s="256"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="250"/>
-      <c r="H12" s="254"/>
+      <c r="G12" s="256"/>
+      <c r="H12" s="245"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -19747,20 +19763,20 @@
       <c r="Z12" s="32"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="83">
+      <c r="A13" s="82">
         <v>7</v>
       </c>
-      <c r="B13" s="256" t="s">
+      <c r="B13" s="263" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="252"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="292" t="s">
+      <c r="C13" s="261"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="251"/>
-      <c r="H13" s="255"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="249"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
@@ -19782,8 +19798,8 @@
     </row>
     <row r="14" spans="1:26" ht="12.75" customHeight="1">
       <c r="A14" s="32"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
@@ -19839,7 +19855,7 @@
       <c r="Z15" s="32"/>
     </row>
     <row r="16" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="79" t="s">
         <v>76</v>
       </c>
       <c r="B16" s="32"/>
@@ -19869,26 +19885,26 @@
       <c r="Z16" s="32"/>
     </row>
     <row r="17" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="226" t="s">
+      <c r="B17" s="258" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="246"/>
-      <c r="D17" s="82" t="s">
+      <c r="C17" s="259"/>
+      <c r="D17" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="234" t="s">
+      <c r="G17" s="253" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="228"/>
+      <c r="H17" s="254"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
@@ -19909,26 +19925,26 @@
       <c r="Z17" s="32"/>
     </row>
     <row r="18" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A18" s="84">
+      <c r="A18" s="83">
         <v>1</v>
       </c>
-      <c r="B18" s="247" t="s">
+      <c r="B18" s="257" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="236"/>
-      <c r="D18" s="86">
-        <v>43830</v>
+      <c r="C18" s="243"/>
+      <c r="D18" s="85">
+        <v>45657</v>
       </c>
-      <c r="E18" s="84" t="s">
+      <c r="E18" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="84" t="s">
+      <c r="F18" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="235" t="s">
+      <c r="G18" s="241" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="236"/>
+      <c r="H18" s="243"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
@@ -19949,24 +19965,24 @@
       <c r="Z18" s="32"/>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A19" s="87">
+      <c r="A19" s="86">
         <v>2</v>
       </c>
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="264" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="238"/>
-      <c r="D19" s="88">
-        <v>43830</v>
+      <c r="C19" s="265"/>
+      <c r="D19" s="87">
+        <v>45657</v>
       </c>
-      <c r="E19" s="87" t="s">
+      <c r="E19" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="87" t="s">
+      <c r="F19" s="86" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="237"/>
-      <c r="H19" s="238"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="265"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
       <c r="K19" s="32"/>
@@ -19987,24 +20003,24 @@
       <c r="Z19" s="32"/>
     </row>
     <row r="20" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A20" s="84">
+      <c r="A20" s="83">
         <v>3</v>
       </c>
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="257" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="236"/>
-      <c r="D20" s="86">
-        <v>43830</v>
+      <c r="C20" s="243"/>
+      <c r="D20" s="85">
+        <v>45657</v>
       </c>
-      <c r="E20" s="84" t="s">
+      <c r="E20" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="84" t="s">
+      <c r="F20" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="235"/>
-      <c r="H20" s="236"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="243"/>
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
       <c r="K20" s="32"/>
@@ -20025,24 +20041,24 @@
       <c r="Z20" s="32"/>
     </row>
     <row r="21" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A21" s="84">
+      <c r="A21" s="83">
         <v>4</v>
       </c>
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="257" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="236"/>
-      <c r="D21" s="86">
-        <v>43830</v>
+      <c r="C21" s="243"/>
+      <c r="D21" s="85">
+        <v>45657</v>
       </c>
-      <c r="E21" s="84" t="s">
+      <c r="E21" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="84" t="s">
+      <c r="F21" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="235"/>
-      <c r="H21" s="236"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="243"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
@@ -20121,7 +20137,7 @@
       <c r="Z23" s="32"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="79" t="s">
         <v>88</v>
       </c>
       <c r="B24" s="32"/>
@@ -20151,22 +20167,22 @@
       <c r="Z24" s="32"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="229" t="s">
+      <c r="B25" s="270" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="189"/>
-      <c r="D25" s="215" t="s">
+      <c r="C25" s="207"/>
+      <c r="D25" s="232" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="188"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="215" t="s">
+      <c r="E25" s="206"/>
+      <c r="F25" s="207"/>
+      <c r="G25" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="189"/>
+      <c r="H25" s="207"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
       <c r="K25" s="32"/>
@@ -20187,16 +20203,16 @@
       <c r="Z25" s="32"/>
     </row>
     <row r="26" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A26" s="90">
+      <c r="A26" s="89">
         <v>1</v>
       </c>
-      <c r="B26" s="230"/>
-      <c r="C26" s="231"/>
-      <c r="D26" s="239"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="231"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="231"/>
+      <c r="B26" s="271"/>
+      <c r="C26" s="272"/>
+      <c r="D26" s="275"/>
+      <c r="E26" s="276"/>
+      <c r="F26" s="272"/>
+      <c r="G26" s="275"/>
+      <c r="H26" s="272"/>
       <c r="I26" s="32"/>
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
@@ -20217,16 +20233,16 @@
       <c r="Z26" s="32"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="91">
+      <c r="A27" s="90">
         <v>2</v>
       </c>
-      <c r="B27" s="232"/>
-      <c r="C27" s="233"/>
-      <c r="D27" s="241"/>
-      <c r="E27" s="242"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="243"/>
-      <c r="H27" s="233"/>
+      <c r="B27" s="273"/>
+      <c r="C27" s="274"/>
+      <c r="D27" s="277"/>
+      <c r="E27" s="278"/>
+      <c r="F27" s="274"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="274"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
@@ -20247,16 +20263,16 @@
       <c r="Z27" s="32"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="92">
+      <c r="A28" s="91">
         <v>3</v>
       </c>
-      <c r="B28" s="224"/>
-      <c r="C28" s="225"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="245"/>
-      <c r="F28" s="225"/>
-      <c r="G28" s="244"/>
-      <c r="H28" s="225"/>
+      <c r="B28" s="267"/>
+      <c r="C28" s="268"/>
+      <c r="D28" s="280"/>
+      <c r="E28" s="281"/>
+      <c r="F28" s="268"/>
+      <c r="G28" s="280"/>
+      <c r="H28" s="268"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
@@ -20335,16 +20351,16 @@
       <c r="Z30" s="32"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="95"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="94"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
@@ -20365,22 +20381,22 @@
       <c r="Z31" s="32"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A32" s="96" t="s">
+      <c r="A32" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="226" t="s">
+      <c r="B32" s="258" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="227"/>
-      <c r="D32" s="228"/>
-      <c r="E32" s="226" t="s">
+      <c r="C32" s="269"/>
+      <c r="D32" s="254"/>
+      <c r="E32" s="258" t="s">
         <v>94</v>
       </c>
-      <c r="F32" s="228"/>
-      <c r="G32" s="226" t="s">
+      <c r="F32" s="254"/>
+      <c r="G32" s="258" t="s">
         <v>95</v>
       </c>
-      <c r="H32" s="228"/>
+      <c r="H32" s="254"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
       <c r="K32" s="32"/>
@@ -20401,22 +20417,22 @@
       <c r="Z32" s="32"/>
     </row>
     <row r="33" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A33" s="97">
+      <c r="A33" s="96">
         <v>1</v>
       </c>
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="241" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="263"/>
-      <c r="D33" s="236"/>
-      <c r="E33" s="235" t="s">
+      <c r="C33" s="242"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="241" t="s">
         <v>97</v>
       </c>
-      <c r="F33" s="236"/>
-      <c r="G33" s="235" t="s">
+      <c r="F33" s="243"/>
+      <c r="G33" s="241" t="s">
         <v>98</v>
       </c>
-      <c r="H33" s="236"/>
+      <c r="H33" s="243"/>
       <c r="I33" s="33"/>
       <c r="J33" s="33"/>
       <c r="K33" s="33"/>
@@ -20437,22 +20453,22 @@
       <c r="Z33" s="33"/>
     </row>
     <row r="34" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A34" s="97">
+      <c r="A34" s="96">
         <v>2</v>
       </c>
-      <c r="B34" s="235" t="s">
+      <c r="B34" s="241" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="263"/>
-      <c r="D34" s="236"/>
-      <c r="E34" s="235" t="s">
+      <c r="C34" s="242"/>
+      <c r="D34" s="243"/>
+      <c r="E34" s="241" t="s">
         <v>100</v>
       </c>
-      <c r="F34" s="236"/>
-      <c r="G34" s="235" t="s">
+      <c r="F34" s="243"/>
+      <c r="G34" s="241" t="s">
         <v>101</v>
       </c>
-      <c r="H34" s="236"/>
+      <c r="H34" s="243"/>
       <c r="I34" s="33"/>
       <c r="J34" s="33"/>
       <c r="K34" s="33"/>
@@ -20473,22 +20489,22 @@
       <c r="Z34" s="33"/>
     </row>
     <row r="35" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A35" s="97">
+      <c r="A35" s="96">
         <v>3</v>
       </c>
-      <c r="B35" s="235" t="s">
+      <c r="B35" s="241" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="263"/>
-      <c r="D35" s="236"/>
-      <c r="E35" s="235" t="s">
+      <c r="C35" s="242"/>
+      <c r="D35" s="243"/>
+      <c r="E35" s="241" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="236"/>
-      <c r="G35" s="235" t="s">
+      <c r="F35" s="243"/>
+      <c r="G35" s="241" t="s">
         <v>104</v>
       </c>
-      <c r="H35" s="236"/>
+      <c r="H35" s="243"/>
       <c r="I35" s="33"/>
       <c r="J35" s="33"/>
       <c r="K35" s="33"/>
@@ -20509,22 +20525,22 @@
       <c r="Z35" s="33"/>
     </row>
     <row r="36" spans="1:26" ht="36" customHeight="1">
-      <c r="A36" s="97">
+      <c r="A36" s="96">
         <v>4</v>
       </c>
-      <c r="B36" s="235" t="s">
+      <c r="B36" s="241" t="s">
         <v>105</v>
       </c>
-      <c r="C36" s="263"/>
-      <c r="D36" s="236"/>
-      <c r="E36" s="235" t="s">
+      <c r="C36" s="242"/>
+      <c r="D36" s="243"/>
+      <c r="E36" s="241" t="s">
         <v>106</v>
       </c>
-      <c r="F36" s="236"/>
-      <c r="G36" s="235" t="s">
+      <c r="F36" s="243"/>
+      <c r="G36" s="241" t="s">
         <v>107</v>
       </c>
-      <c r="H36" s="236"/>
+      <c r="H36" s="243"/>
       <c r="I36" s="33"/>
       <c r="J36" s="33"/>
       <c r="K36" s="33"/>
@@ -20545,22 +20561,22 @@
       <c r="Z36" s="33"/>
     </row>
     <row r="37" spans="1:26" ht="36" customHeight="1">
-      <c r="A37" s="97">
+      <c r="A37" s="96">
         <v>5</v>
       </c>
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="C37" s="263"/>
-      <c r="D37" s="236"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="242"/>
+      <c r="D37" s="243"/>
+      <c r="E37" s="241" t="s">
         <v>100</v>
       </c>
-      <c r="F37" s="236"/>
-      <c r="G37" s="235" t="s">
+      <c r="F37" s="243"/>
+      <c r="G37" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="H37" s="236"/>
+      <c r="H37" s="243"/>
       <c r="I37" s="33"/>
       <c r="J37" s="33"/>
       <c r="K37" s="33"/>
@@ -20639,7 +20655,7 @@
       <c r="Z39" s="32"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="79" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="32"/>
@@ -20669,20 +20685,20 @@
       <c r="Z40" s="32"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A41" s="98" t="s">
+      <c r="A41" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="258" t="s">
+      <c r="B41" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="189"/>
-      <c r="D41" s="215" t="s">
+      <c r="C41" s="207"/>
+      <c r="D41" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="188"/>
-      <c r="F41" s="188"/>
-      <c r="G41" s="188"/>
-      <c r="H41" s="189"/>
+      <c r="E41" s="206"/>
+      <c r="F41" s="206"/>
+      <c r="G41" s="206"/>
+      <c r="H41" s="207"/>
       <c r="I41" s="32"/>
       <c r="J41" s="32"/>
       <c r="K41" s="32"/>
@@ -20703,16 +20719,16 @@
       <c r="Z41" s="32"/>
     </row>
     <row r="42" spans="1:26" ht="15" customHeight="1">
-      <c r="A42" s="99">
+      <c r="A42" s="98">
         <v>1</v>
       </c>
-      <c r="B42" s="259"/>
-      <c r="C42" s="254"/>
-      <c r="D42" s="259"/>
-      <c r="E42" s="263"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="263"/>
-      <c r="H42" s="254"/>
+      <c r="B42" s="247"/>
+      <c r="C42" s="245"/>
+      <c r="D42" s="247"/>
+      <c r="E42" s="242"/>
+      <c r="F42" s="242"/>
+      <c r="G42" s="242"/>
+      <c r="H42" s="245"/>
       <c r="I42" s="32"/>
       <c r="J42" s="32"/>
       <c r="K42" s="32"/>
@@ -20733,16 +20749,16 @@
       <c r="Z42" s="32"/>
     </row>
     <row r="43" spans="1:26" ht="15" customHeight="1">
-      <c r="A43" s="100">
+      <c r="A43" s="99">
         <v>2</v>
       </c>
-      <c r="B43" s="260"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="260"/>
-      <c r="E43" s="264"/>
-      <c r="F43" s="264"/>
-      <c r="G43" s="264"/>
-      <c r="H43" s="255"/>
+      <c r="B43" s="248"/>
+      <c r="C43" s="249"/>
+      <c r="D43" s="248"/>
+      <c r="E43" s="252"/>
+      <c r="F43" s="252"/>
+      <c r="G43" s="252"/>
+      <c r="H43" s="249"/>
       <c r="I43" s="32"/>
       <c r="J43" s="32"/>
       <c r="K43" s="32"/>
@@ -20821,7 +20837,7 @@
       <c r="Z45" s="32"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="79" t="s">
         <v>114</v>
       </c>
       <c r="B46" s="32"/>
@@ -20851,24 +20867,24 @@
       <c r="Z46" s="32"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A47" s="98" t="s">
+      <c r="A47" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="215" t="s">
+      <c r="B47" s="232" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="189"/>
-      <c r="D47" s="215" t="s">
+      <c r="C47" s="207"/>
+      <c r="D47" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="189"/>
-      <c r="F47" s="101" t="s">
+      <c r="E47" s="207"/>
+      <c r="F47" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="G47" s="101" t="s">
+      <c r="G47" s="100" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="101" t="s">
+      <c r="H47" s="100" t="s">
         <v>117</v>
       </c>
       <c r="I47" s="32"/>
@@ -20891,16 +20907,16 @@
       <c r="Z47" s="32"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A48" s="102">
+      <c r="A48" s="101">
         <v>1</v>
       </c>
-      <c r="B48" s="261"/>
-      <c r="C48" s="262"/>
-      <c r="D48" s="261"/>
-      <c r="E48" s="262"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
+      <c r="B48" s="250"/>
+      <c r="C48" s="251"/>
+      <c r="D48" s="250"/>
+      <c r="E48" s="251"/>
+      <c r="F48" s="102"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
       <c r="I48" s="33"/>
       <c r="J48" s="33"/>
       <c r="K48" s="33"/>
@@ -20921,16 +20937,16 @@
       <c r="Z48" s="33"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A49" s="105">
+      <c r="A49" s="104">
         <v>2</v>
       </c>
-      <c r="B49" s="257"/>
-      <c r="C49" s="254"/>
-      <c r="D49" s="257"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="106"/>
-      <c r="G49" s="104"/>
-      <c r="H49" s="104"/>
+      <c r="B49" s="244"/>
+      <c r="C49" s="245"/>
+      <c r="D49" s="244"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
       <c r="I49" s="33"/>
       <c r="J49" s="33"/>
       <c r="K49" s="33"/>
@@ -20951,16 +20967,16 @@
       <c r="Z49" s="33"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A50" s="102">
+      <c r="A50" s="101">
         <v>3</v>
       </c>
-      <c r="B50" s="257"/>
-      <c r="C50" s="254"/>
-      <c r="D50" s="257"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="106"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
+      <c r="B50" s="244"/>
+      <c r="C50" s="245"/>
+      <c r="D50" s="244"/>
+      <c r="E50" s="245"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="103"/>
       <c r="I50" s="33"/>
       <c r="J50" s="33"/>
       <c r="K50" s="33"/>
@@ -20985,8 +21001,8 @@
       <c r="B51" s="32"/>
       <c r="C51" s="32"/>
       <c r="D51" s="32"/>
-      <c r="E51" s="107"/>
-      <c r="F51" s="107"/>
+      <c r="E51" s="106"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="32"/>
       <c r="H51" s="32"/>
       <c r="I51" s="32"/>
@@ -27332,6 +27348,68 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="G34:H34"/>
@@ -27348,68 +27426,6 @@
     <mergeCell ref="D42:H42"/>
     <mergeCell ref="D43:H43"/>
     <mergeCell ref="D41:H41"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:H28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -27423,15 +27439,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" customWidth="1"/>
-    <col min="5" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.1640625" customWidth="1"/>
+    <col min="5" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" customWidth="1"/>
+    <col min="8" max="8" width="27.1640625" customWidth="1"/>
     <col min="9" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27467,11 +27483,11 @@
       <c r="A2" s="32"/>
       <c r="B2" s="32"/>
       <c r="C2" s="34"/>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
       <c r="G2" s="34"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
@@ -27699,23 +27715,23 @@
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
       <c r="A10" s="32"/>
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="107" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="273" t="s">
+      <c r="C10" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="275" t="s">
+      <c r="D10" s="285" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="275" t="s">
+      <c r="E10" s="285" t="s">
         <v>125</v>
       </c>
-      <c r="F10" s="276" t="s">
+      <c r="F10" s="286" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="277"/>
-      <c r="H10" s="279"/>
+      <c r="G10" s="287"/>
+      <c r="H10" s="289"/>
       <c r="I10" s="32"/>
       <c r="J10" s="32"/>
       <c r="K10" s="32"/>
@@ -27737,15 +27753,15 @@
     </row>
     <row r="11" spans="1:26" ht="22.5" customHeight="1">
       <c r="A11" s="32"/>
-      <c r="B11" s="109" t="s">
+      <c r="B11" s="108" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="274"/>
-      <c r="D11" s="274"/>
-      <c r="E11" s="274"/>
-      <c r="F11" s="274"/>
-      <c r="G11" s="278"/>
-      <c r="H11" s="280"/>
+      <c r="C11" s="284"/>
+      <c r="D11" s="284"/>
+      <c r="E11" s="284"/>
+      <c r="F11" s="284"/>
+      <c r="G11" s="288"/>
+      <c r="H11" s="290"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
       <c r="K11" s="32"/>
@@ -27767,19 +27783,21 @@
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
       <c r="A12" s="32"/>
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="109" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="101" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="102" t="s">
-        <v>129</v>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101" t="s">
+        <v>128</v>
       </c>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102" t="s">
-        <v>129</v>
+      <c r="F12" s="101"/>
+      <c r="G12" s="323" t="s">
+        <v>204</v>
       </c>
-      <c r="F12" s="102"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="112"/>
+      <c r="H12" s="110"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -27801,21 +27819,23 @@
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
       <c r="A13" s="32"/>
-      <c r="B13" s="110" t="s">
-        <v>130</v>
+      <c r="B13" s="109" t="s">
+        <v>206</v>
       </c>
-      <c r="C13" s="105"/>
-      <c r="D13" s="105" t="s">
-        <v>129</v>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104" t="s">
+        <v>128</v>
       </c>
-      <c r="E13" s="105" t="s">
-        <v>129</v>
+      <c r="E13" s="104" t="s">
+        <v>128</v>
       </c>
-      <c r="F13" s="105" t="s">
-        <v>129</v>
+      <c r="F13" s="104" t="s">
+        <v>128</v>
       </c>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
+      <c r="G13" s="323" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" s="111"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
@@ -27837,23 +27857,23 @@
     </row>
     <row r="14" spans="1:26" ht="24.75" customHeight="1">
       <c r="A14" s="32"/>
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="72" t="s">
-        <v>131</v>
+      <c r="C14" s="71" t="s">
+        <v>129</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="72" t="s">
+      <c r="E14" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
@@ -27875,11 +27895,11 @@
     </row>
     <row r="15" spans="1:26" ht="12.75" customHeight="1">
       <c r="A15" s="32"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
@@ -27903,11 +27923,11 @@
     </row>
     <row r="16" spans="1:26" ht="12.75" customHeight="1">
       <c r="A16" s="32"/>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="116"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
@@ -27932,7 +27952,7 @@
     <row r="17" spans="1:26" ht="12.75" customHeight="1">
       <c r="A17" s="32"/>
       <c r="B17" s="35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -27962,7 +27982,7 @@
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="32"/>
       <c r="B18" s="37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -27991,19 +28011,19 @@
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1">
       <c r="A19" s="32"/>
-      <c r="B19" s="215" t="s">
-        <v>134</v>
+      <c r="B19" s="232" t="s">
+        <v>132</v>
       </c>
-      <c r="C19" s="189"/>
-      <c r="D19" s="215" t="s">
-        <v>135</v>
+      <c r="C19" s="207"/>
+      <c r="D19" s="232" t="s">
+        <v>133</v>
       </c>
-      <c r="E19" s="188"/>
-      <c r="F19" s="272"/>
-      <c r="G19" s="215" t="s">
+      <c r="E19" s="206"/>
+      <c r="F19" s="282"/>
+      <c r="G19" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="189"/>
+      <c r="H19" s="207"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
       <c r="K19" s="32"/>
@@ -28025,15 +28045,15 @@
     </row>
     <row r="20" spans="1:26" ht="51" customHeight="1">
       <c r="A20" s="33"/>
-      <c r="B20" s="268" t="s">
-        <v>186</v>
+      <c r="B20" s="291" t="s">
+        <v>184</v>
       </c>
-      <c r="C20" s="189"/>
-      <c r="D20" s="268"/>
-      <c r="E20" s="188"/>
-      <c r="F20" s="188"/>
-      <c r="G20" s="271"/>
-      <c r="H20" s="189"/>
+      <c r="C20" s="207"/>
+      <c r="D20" s="291"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="206"/>
+      <c r="G20" s="292"/>
+      <c r="H20" s="207"/>
       <c r="I20" s="33"/>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
@@ -28112,7 +28132,7 @@
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="32"/>
       <c r="B23" s="35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="33"/>
@@ -28142,7 +28162,7 @@
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="32"/>
       <c r="B24" s="37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C24" s="33"/>
       <c r="D24" s="33"/>
@@ -28171,19 +28191,19 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="33"/>
-      <c r="B25" s="98" t="s">
+      <c r="B25" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="C25" s="215" t="s">
-        <v>138</v>
+      <c r="C25" s="232" t="s">
+        <v>136</v>
       </c>
-      <c r="D25" s="188"/>
-      <c r="E25" s="188"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="258" t="s">
+      <c r="D25" s="206"/>
+      <c r="E25" s="206"/>
+      <c r="F25" s="207"/>
+      <c r="G25" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="189"/>
+      <c r="H25" s="207"/>
       <c r="I25" s="33"/>
       <c r="J25" s="33"/>
       <c r="K25" s="33"/>
@@ -28205,17 +28225,17 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="32"/>
-      <c r="B26" s="65" t="s">
-        <v>139</v>
+      <c r="B26" s="64" t="s">
+        <v>137</v>
       </c>
-      <c r="C26" s="265" t="s">
-        <v>180</v>
+      <c r="C26" s="293" t="s">
+        <v>178</v>
       </c>
-      <c r="D26" s="188"/>
-      <c r="E26" s="188"/>
-      <c r="F26" s="189"/>
-      <c r="G26" s="266"/>
-      <c r="H26" s="189"/>
+      <c r="D26" s="206"/>
+      <c r="E26" s="206"/>
+      <c r="F26" s="207"/>
+      <c r="G26" s="294"/>
+      <c r="H26" s="207"/>
       <c r="I26" s="32"/>
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
@@ -28237,17 +28257,17 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="32"/>
-      <c r="B27" s="65" t="s">
-        <v>140</v>
+      <c r="B27" s="64" t="s">
+        <v>138</v>
       </c>
-      <c r="C27" s="268" t="s">
-        <v>181</v>
+      <c r="C27" s="291" t="s">
+        <v>179</v>
       </c>
-      <c r="D27" s="188"/>
-      <c r="E27" s="188"/>
-      <c r="F27" s="189"/>
-      <c r="G27" s="269"/>
-      <c r="H27" s="189"/>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="207"/>
+      <c r="G27" s="297"/>
+      <c r="H27" s="207"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
@@ -28269,17 +28289,17 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="32"/>
-      <c r="B28" s="65" t="s">
-        <v>141</v>
+      <c r="B28" s="64" t="s">
+        <v>139</v>
       </c>
-      <c r="C28" s="268" t="s">
-        <v>182</v>
+      <c r="C28" s="291" t="s">
+        <v>180</v>
       </c>
-      <c r="D28" s="188"/>
-      <c r="E28" s="188"/>
-      <c r="F28" s="189"/>
-      <c r="G28" s="266"/>
-      <c r="H28" s="189"/>
+      <c r="D28" s="206"/>
+      <c r="E28" s="206"/>
+      <c r="F28" s="207"/>
+      <c r="G28" s="294"/>
+      <c r="H28" s="207"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
@@ -28301,17 +28321,17 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="32"/>
-      <c r="B29" s="117" t="s">
-        <v>142</v>
+      <c r="B29" s="115" t="s">
+        <v>140</v>
       </c>
-      <c r="C29" s="270" t="s">
-        <v>183</v>
+      <c r="C29" s="298" t="s">
+        <v>181</v>
       </c>
-      <c r="D29" s="188"/>
-      <c r="E29" s="188"/>
-      <c r="F29" s="189"/>
-      <c r="G29" s="267"/>
-      <c r="H29" s="189"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="207"/>
+      <c r="G29" s="296"/>
+      <c r="H29" s="207"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
       <c r="K29" s="32"/>
@@ -28333,17 +28353,17 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="32"/>
-      <c r="B30" s="118" t="s">
-        <v>143</v>
+      <c r="B30" s="116" t="s">
+        <v>141</v>
       </c>
-      <c r="C30" s="293" t="s">
-        <v>184</v>
+      <c r="C30" s="295" t="s">
+        <v>182</v>
       </c>
-      <c r="D30" s="188"/>
-      <c r="E30" s="188"/>
-      <c r="F30" s="189"/>
-      <c r="G30" s="267"/>
-      <c r="H30" s="189"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="207"/>
+      <c r="G30" s="296"/>
+      <c r="H30" s="207"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
@@ -28365,17 +28385,17 @@
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
       <c r="A31" s="32"/>
-      <c r="B31" s="117" t="s">
-        <v>144</v>
+      <c r="B31" s="115" t="s">
+        <v>142</v>
       </c>
-      <c r="C31" s="268" t="s">
-        <v>185</v>
+      <c r="C31" s="291" t="s">
+        <v>183</v>
       </c>
-      <c r="D31" s="188"/>
-      <c r="E31" s="188"/>
-      <c r="F31" s="189"/>
-      <c r="G31" s="267"/>
-      <c r="H31" s="189"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="206"/>
+      <c r="F31" s="207"/>
+      <c r="G31" s="296"/>
+      <c r="H31" s="207"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
@@ -28481,8 +28501,8 @@
     </row>
     <row r="35" spans="1:26" ht="12.75" customHeight="1">
       <c r="A35" s="32"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="119"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="117"/>
       <c r="D35" s="33"/>
       <c r="E35" s="33"/>
       <c r="F35" s="33"/>
@@ -28566,7 +28586,7 @@
     <row r="38" spans="1:26" ht="12.75" customHeight="1">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
-      <c r="C38" s="119"/>
+      <c r="C38" s="117"/>
       <c r="D38" s="33"/>
       <c r="E38" s="33"/>
       <c r="F38" s="33"/>
@@ -34766,20 +34786,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:H25"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="C30:F30"/>
@@ -34792,6 +34798,20 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="G30:H30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -34806,16 +34826,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:X995"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" customWidth="1"/>
     <col min="7" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="48.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
+    <col min="12" max="12" width="48.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.1640625" customWidth="1"/>
     <col min="14" max="24" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -34848,11 +34868,11 @@
     <row r="2" spans="1:24" ht="30" customHeight="1">
       <c r="A2" s="32"/>
       <c r="B2" s="32"/>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="32"/>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
@@ -34901,12 +34921,12 @@
     </row>
     <row r="4" spans="1:24" ht="12.75" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -34929,7 +34949,7 @@
     </row>
     <row r="5" spans="1:24" ht="12.75" customHeight="1">
       <c r="A5" s="37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
@@ -34956,24 +34976,24 @@
       <c r="X5" s="32"/>
     </row>
     <row r="6" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="120" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="121" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="232" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="123" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="215" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="188"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="189"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="207"/>
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
       <c r="M6" s="32"/>
@@ -34990,26 +35010,26 @@
       <c r="X6" s="32"/>
     </row>
     <row r="7" spans="1:24" ht="69.599999999999994" customHeight="1">
-      <c r="A7" s="124">
+      <c r="A7" s="122">
         <f t="shared" ref="A7:A11" si="0">ROW()-6</f>
         <v>1</v>
       </c>
-      <c r="B7" s="125" t="str">
+      <c r="B7" s="123" t="str">
         <f>Appendix!C48</f>
         <v>Đỗ Việt Cường - 21130299</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>150</v>
+      <c r="C7" s="52" t="s">
+        <v>148</v>
       </c>
-      <c r="D7" s="298" t="s">
-        <v>187</v>
+      <c r="D7" s="299" t="s">
+        <v>185</v>
       </c>
-      <c r="E7" s="218"/>
-      <c r="F7" s="218"/>
-      <c r="G7" s="218"/>
-      <c r="H7" s="218"/>
-      <c r="I7" s="218"/>
-      <c r="J7" s="281"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="235"/>
+      <c r="H7" s="235"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="300"/>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
@@ -35026,26 +35046,26 @@
       <c r="X7" s="32"/>
     </row>
     <row r="8" spans="1:24" ht="42.6" customHeight="1">
-      <c r="A8" s="124">
+      <c r="A8" s="122">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B8" s="113" t="str">
+      <c r="B8" s="111" t="str">
         <f>Appendix!C49</f>
         <v>Lâm Trạch Đông - 21130317</v>
       </c>
-      <c r="C8" s="56" t="s">
-        <v>151</v>
+      <c r="C8" s="55" t="s">
+        <v>149</v>
       </c>
-      <c r="D8" s="299" t="s">
-        <v>188</v>
+      <c r="D8" s="301" t="s">
+        <v>186</v>
       </c>
-      <c r="E8" s="218"/>
-      <c r="F8" s="218"/>
-      <c r="G8" s="218"/>
-      <c r="H8" s="218"/>
-      <c r="I8" s="218"/>
-      <c r="J8" s="281"/>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="300"/>
       <c r="K8" s="32"/>
       <c r="L8" s="32"/>
       <c r="M8" s="32"/>
@@ -35062,26 +35082,26 @@
       <c r="X8" s="32"/>
     </row>
     <row r="9" spans="1:24" ht="45" customHeight="1">
-      <c r="A9" s="124">
+      <c r="A9" s="122">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B9" s="113" t="str">
+      <c r="B9" s="111" t="str">
         <f>Appendix!C52</f>
         <v>Trần Văn Triều - 21130639</v>
       </c>
-      <c r="C9" s="56" t="s">
-        <v>151</v>
+      <c r="C9" s="55" t="s">
+        <v>149</v>
       </c>
-      <c r="D9" s="299" t="s">
-        <v>189</v>
+      <c r="D9" s="301" t="s">
+        <v>187</v>
       </c>
-      <c r="E9" s="218"/>
-      <c r="F9" s="218"/>
-      <c r="G9" s="218"/>
-      <c r="H9" s="218"/>
-      <c r="I9" s="218"/>
-      <c r="J9" s="281"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="300"/>
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
       <c r="M9" s="32"/>
@@ -35098,26 +35118,26 @@
       <c r="X9" s="32"/>
     </row>
     <row r="10" spans="1:24" ht="54.6" customHeight="1">
-      <c r="A10" s="124">
+      <c r="A10" s="122">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" s="126" t="str">
+      <c r="B10" s="124" t="str">
         <f>Appendix!C51</f>
         <v>Phạm Nhựt Tân - 21130530</v>
       </c>
-      <c r="C10" s="56" t="s">
-        <v>151</v>
+      <c r="C10" s="55" t="s">
+        <v>149</v>
       </c>
-      <c r="D10" s="299" t="s">
-        <v>190</v>
+      <c r="D10" s="301" t="s">
+        <v>188</v>
       </c>
-      <c r="E10" s="218"/>
-      <c r="F10" s="218"/>
-      <c r="G10" s="218"/>
-      <c r="H10" s="218"/>
-      <c r="I10" s="218"/>
-      <c r="J10" s="281"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="300"/>
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
       <c r="M10" s="32"/>
@@ -35133,27 +35153,27 @@
       <c r="W10" s="32"/>
       <c r="X10" s="32"/>
     </row>
-    <row r="11" spans="1:24" ht="49.8" customHeight="1">
-      <c r="A11" s="294">
+    <row r="11" spans="1:24" ht="49.9" customHeight="1">
+      <c r="A11" s="180">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="295" t="str">
+      <c r="B11" s="181" t="str">
         <f>Appendix!C50</f>
         <v>Nguyễn Quốc Anh Tuấn - 21130601</v>
       </c>
-      <c r="C11" s="318" t="s">
-        <v>200</v>
+      <c r="C11" s="189" t="s">
+        <v>198</v>
       </c>
-      <c r="D11" s="300" t="s">
-        <v>191</v>
+      <c r="D11" s="302" t="s">
+        <v>189</v>
       </c>
-      <c r="E11" s="296"/>
-      <c r="F11" s="296"/>
-      <c r="G11" s="296"/>
-      <c r="H11" s="296"/>
-      <c r="I11" s="296"/>
-      <c r="J11" s="297"/>
+      <c r="E11" s="303"/>
+      <c r="F11" s="303"/>
+      <c r="G11" s="303"/>
+      <c r="H11" s="303"/>
+      <c r="I11" s="303"/>
+      <c r="J11" s="304"/>
       <c r="K11" s="32"/>
       <c r="L11" s="32"/>
       <c r="M11" s="32"/>
@@ -35170,11 +35190,11 @@
       <c r="X11" s="32"/>
     </row>
     <row r="12" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
@@ -35250,19 +35270,19 @@
       <c r="X14" s="32"/>
     </row>
     <row r="15" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="96" t="s">
-        <v>152</v>
+      <c r="B15" s="95" t="s">
+        <v>150</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="215" t="s">
+      <c r="D15" s="232" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="189"/>
+      <c r="E15" s="207"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
@@ -35284,26 +35304,26 @@
       <c r="X15" s="32"/>
     </row>
     <row r="16" spans="1:24" ht="12" customHeight="1">
-      <c r="A16" s="90">
+      <c r="A16" s="89">
         <v>1</v>
       </c>
-      <c r="B16" s="130" t="s">
+      <c r="B16" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="131">
+      <c r="C16" s="129">
         <v>45591</v>
       </c>
-      <c r="D16" s="282">
+      <c r="D16" s="305">
         <v>45592</v>
       </c>
-      <c r="E16" s="283"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="32"/>
-      <c r="L16" s="132"/>
+      <c r="L16" s="130"/>
       <c r="M16" s="32"/>
       <c r="N16" s="32"/>
       <c r="O16" s="32"/>
@@ -35318,19 +35338,19 @@
       <c r="X16" s="32"/>
     </row>
     <row r="17" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A17" s="91">
+      <c r="A17" s="90">
         <v>2</v>
       </c>
-      <c r="B17" s="133" t="s">
+      <c r="B17" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="131">
+      <c r="C17" s="129">
         <v>45591</v>
       </c>
-      <c r="D17" s="282">
+      <c r="D17" s="305">
         <v>45593</v>
       </c>
-      <c r="E17" s="283"/>
+      <c r="E17" s="306"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -35352,26 +35372,26 @@
       <c r="X17" s="32"/>
     </row>
     <row r="18" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A18" s="91">
+      <c r="A18" s="90">
         <v>3</v>
       </c>
-      <c r="B18" s="133" t="s">
-        <v>153</v>
+      <c r="B18" s="131" t="s">
+        <v>151</v>
       </c>
-      <c r="C18" s="131">
+      <c r="C18" s="129">
         <v>45592</v>
       </c>
-      <c r="D18" s="282">
+      <c r="D18" s="305">
         <v>45594</v>
       </c>
-      <c r="E18" s="283"/>
+      <c r="E18" s="306"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
-      <c r="L18" s="132"/>
+      <c r="L18" s="130"/>
       <c r="M18" s="32"/>
       <c r="N18" s="32"/>
       <c r="O18" s="32"/>
@@ -35386,19 +35406,19 @@
       <c r="X18" s="32"/>
     </row>
     <row r="19" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A19" s="134">
+      <c r="A19" s="132">
         <v>4</v>
       </c>
-      <c r="B19" s="135" t="s">
-        <v>154</v>
+      <c r="B19" s="133" t="s">
+        <v>152</v>
       </c>
-      <c r="C19" s="131">
+      <c r="C19" s="129">
         <v>45592</v>
       </c>
-      <c r="D19" s="282">
+      <c r="D19" s="305">
         <v>45596</v>
       </c>
-      <c r="E19" s="283"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
@@ -35420,19 +35440,19 @@
       <c r="X19" s="32"/>
     </row>
     <row r="20" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A20" s="136">
+      <c r="A20" s="134">
         <v>5</v>
       </c>
-      <c r="B20" s="137" t="s">
-        <v>155</v>
+      <c r="B20" s="135" t="s">
+        <v>153</v>
       </c>
-      <c r="C20" s="315">
+      <c r="C20" s="186">
         <v>45596</v>
       </c>
-      <c r="D20" s="282">
+      <c r="D20" s="305">
         <v>45596</v>
       </c>
-      <c r="E20" s="283"/>
+      <c r="E20" s="306"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
@@ -35454,19 +35474,19 @@
       <c r="X20" s="32"/>
     </row>
     <row r="21" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A21" s="138">
+      <c r="A21" s="136">
         <v>6</v>
       </c>
-      <c r="B21" s="139" t="s">
-        <v>156</v>
+      <c r="B21" s="137" t="s">
+        <v>154</v>
       </c>
-      <c r="C21" s="301">
+      <c r="C21" s="182">
         <v>45597</v>
       </c>
-      <c r="D21" s="302">
+      <c r="D21" s="307">
         <v>45597</v>
       </c>
-      <c r="E21" s="303"/>
+      <c r="E21" s="308"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
@@ -35514,17 +35534,17 @@
       <c r="X22" s="32"/>
     </row>
     <row r="23" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A23" s="140"/>
-      <c r="B23" s="96" t="s">
-        <v>157</v>
+      <c r="A23" s="138"/>
+      <c r="B23" s="95" t="s">
+        <v>155</v>
       </c>
-      <c r="C23" s="317" t="s">
-        <v>199</v>
+      <c r="C23" s="188" t="s">
+        <v>197</v>
       </c>
-      <c r="D23" s="81" t="s">
-        <v>158</v>
+      <c r="D23" s="80" t="s">
+        <v>156</v>
       </c>
-      <c r="E23" s="141"/>
+      <c r="E23" s="139"/>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
@@ -35547,14 +35567,14 @@
     </row>
     <row r="24" spans="1:24" ht="12.75" customHeight="1">
       <c r="A24" s="32"/>
-      <c r="B24" s="142" t="s">
+      <c r="B24" s="140" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="143">
+      <c r="C24" s="141">
         <f>INT(C16)-INT($C$16)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="143">
+      <c r="D24" s="141">
         <f t="shared" ref="D24:D28" si="1">(INT(D16)-INT($C$16))-(INT(C16)-INT($C$16))</f>
         <v>1</v>
       </c>
@@ -35566,7 +35586,7 @@
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
       <c r="L24" s="32"/>
-      <c r="M24" s="144"/>
+      <c r="M24" s="142"/>
       <c r="N24" s="32"/>
       <c r="O24" s="32"/>
       <c r="P24" s="32"/>
@@ -35581,14 +35601,14 @@
     </row>
     <row r="25" spans="1:24" ht="12.75" customHeight="1">
       <c r="A25" s="32"/>
-      <c r="B25" s="142" t="s">
+      <c r="B25" s="140" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="143">
+      <c r="C25" s="141">
         <f>INT(C17)-INT($C$16)-1</f>
         <v>-1</v>
       </c>
-      <c r="D25" s="143">
+      <c r="D25" s="141">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -35615,14 +35635,14 @@
     </row>
     <row r="26" spans="1:24" ht="12.75" customHeight="1">
       <c r="A26" s="32"/>
-      <c r="B26" s="142" t="s">
-        <v>153</v>
+      <c r="B26" s="140" t="s">
+        <v>151</v>
       </c>
-      <c r="C26" s="143">
+      <c r="C26" s="141">
         <f>INT(C18)-INT($C$16)-2</f>
         <v>-1</v>
       </c>
-      <c r="D26" s="143">
+      <c r="D26" s="141">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -35649,14 +35669,14 @@
     </row>
     <row r="27" spans="1:24" ht="12.75" customHeight="1">
       <c r="A27" s="32"/>
-      <c r="B27" s="142" t="s">
-        <v>154</v>
+      <c r="B27" s="140" t="s">
+        <v>152</v>
       </c>
-      <c r="C27" s="143">
+      <c r="C27" s="141">
         <f>INT(C19)-INT($C$16)-3</f>
         <v>-2</v>
       </c>
-      <c r="D27" s="143">
+      <c r="D27" s="141">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -35683,14 +35703,14 @@
     </row>
     <row r="28" spans="1:24" ht="12.75" customHeight="1">
       <c r="A28" s="32"/>
-      <c r="B28" s="142" t="s">
-        <v>155</v>
+      <c r="B28" s="140" t="s">
+        <v>153</v>
       </c>
-      <c r="C28" s="143">
+      <c r="C28" s="141">
         <f>INT(C20)-INT($C$16)-4</f>
         <v>1</v>
       </c>
-      <c r="D28" s="143">
+      <c r="D28" s="141">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -35717,14 +35737,14 @@
     </row>
     <row r="29" spans="1:24" ht="12.75" customHeight="1">
       <c r="A29" s="32"/>
-      <c r="B29" s="142" t="s">
-        <v>156</v>
+      <c r="B29" s="140" t="s">
+        <v>154</v>
       </c>
-      <c r="C29" s="143">
+      <c r="C29" s="141">
         <f>INT(C21)-INT($C$16)-5</f>
         <v>1</v>
       </c>
-      <c r="D29" s="143">
+      <c r="D29" s="141">
         <f>(INT(D21)-INT($C$16))-(INT(C21)-INT($C$16))+1</f>
         <v>1</v>
       </c>
@@ -35777,7 +35797,7 @@
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1">
       <c r="A31" s="35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B31" s="35"/>
       <c r="C31" s="32"/>
@@ -35805,11 +35825,11 @@
     </row>
     <row r="32" spans="1:24" ht="12.75" customHeight="1">
       <c r="A32" s="32"/>
-      <c r="B32" s="145" t="s">
-        <v>160</v>
+      <c r="B32" s="143" t="s">
+        <v>158</v>
       </c>
       <c r="C32" s="32"/>
-      <c r="D32" s="146"/>
+      <c r="D32" s="144"/>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
@@ -41796,11 +41816,6 @@
     <row r="995" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
@@ -41809,6 +41824,11 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B32" location="Detail Schedule!A1" display="Liên kết" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -41828,77 +41848,77 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC985"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" customWidth="1"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="41.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="3.85546875" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
+    <col min="6" max="6" width="3.83203125" customWidth="1"/>
+    <col min="7" max="7" width="4.5" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" customWidth="1"/>
     <col min="9" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" customWidth="1"/>
-    <col min="13" max="13" width="4.28515625" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" customWidth="1"/>
-    <col min="17" max="18" width="3.5703125" customWidth="1"/>
+    <col min="12" max="12" width="4.1640625" customWidth="1"/>
+    <col min="13" max="13" width="4.33203125" customWidth="1"/>
+    <col min="14" max="14" width="3.1640625" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="16" max="16" width="3.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.5" customWidth="1"/>
     <col min="19" max="19" width="4" customWidth="1"/>
-    <col min="20" max="20" width="3.7109375" customWidth="1"/>
-    <col min="21" max="21" width="4.28515625" customWidth="1"/>
-    <col min="22" max="22" width="4.140625" customWidth="1"/>
-    <col min="23" max="23" width="3.85546875" customWidth="1"/>
-    <col min="24" max="24" width="4.42578125" customWidth="1"/>
-    <col min="25" max="25" width="4.7109375" customWidth="1"/>
-    <col min="26" max="26" width="4.5703125" customWidth="1"/>
+    <col min="20" max="20" width="3.6640625" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
+    <col min="22" max="22" width="4.1640625" customWidth="1"/>
+    <col min="23" max="23" width="3.83203125" customWidth="1"/>
+    <col min="24" max="24" width="4.5" customWidth="1"/>
+    <col min="25" max="25" width="4.6640625" customWidth="1"/>
+    <col min="26" max="26" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="312" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="286" t="s">
-        <v>152</v>
+      <c r="B1" s="314" t="s">
+        <v>150</v>
       </c>
-      <c r="C1" s="288" t="s">
-        <v>149</v>
+      <c r="C1" s="316" t="s">
+        <v>147</v>
       </c>
-      <c r="D1" s="304" t="s">
-        <v>192</v>
+      <c r="D1" s="318" t="s">
+        <v>190</v>
       </c>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="305"/>
-      <c r="H1" s="305"/>
-      <c r="I1" s="305"/>
-      <c r="J1" s="304" t="s">
-        <v>193</v>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="318" t="s">
+        <v>191</v>
       </c>
-      <c r="K1" s="305"/>
-      <c r="L1" s="305"/>
-      <c r="M1" s="305"/>
-      <c r="N1" s="305"/>
-      <c r="O1" s="305"/>
-      <c r="P1" s="305"/>
-      <c r="Q1" s="305"/>
-      <c r="R1" s="305"/>
-      <c r="S1" s="308"/>
-      <c r="T1" s="308"/>
-      <c r="U1" s="308"/>
-      <c r="V1" s="308"/>
-      <c r="W1" s="308"/>
-      <c r="X1" s="308"/>
-      <c r="Y1" s="308"/>
-      <c r="Z1" s="308"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="185"/>
+      <c r="T1" s="185"/>
+      <c r="U1" s="185"/>
+      <c r="V1" s="185"/>
+      <c r="W1" s="185"/>
+      <c r="X1" s="185"/>
+      <c r="Y1" s="185"/>
+      <c r="Z1" s="185"/>
       <c r="AB1" s="32"/>
       <c r="AC1" s="32"/>
     </row>
     <row r="2" spans="1:29" ht="12" customHeight="1">
-      <c r="A2" s="285"/>
-      <c r="B2" s="287"/>
-      <c r="C2" s="289"/>
+      <c r="A2" s="313"/>
+      <c r="B2" s="315"/>
+      <c r="C2" s="317"/>
       <c r="D2" s="32">
         <v>26</v>
       </c>
@@ -41944,583 +41964,583 @@
       <c r="R2" s="32">
         <v>9</v>
       </c>
-      <c r="S2" s="308"/>
-      <c r="T2" s="308"/>
-      <c r="U2" s="308"/>
-      <c r="V2" s="308"/>
-      <c r="W2" s="308"/>
-      <c r="X2" s="308"/>
-      <c r="Y2" s="308"/>
-      <c r="Z2" s="308"/>
+      <c r="S2" s="185"/>
+      <c r="T2" s="185"/>
+      <c r="U2" s="185"/>
+      <c r="V2" s="185"/>
+      <c r="W2" s="185"/>
+      <c r="X2" s="185"/>
+      <c r="Y2" s="185"/>
+      <c r="Z2" s="185"/>
       <c r="AB2" s="32"/>
       <c r="AC2" s="32"/>
     </row>
     <row r="3" spans="1:29" ht="14.25" customHeight="1">
-      <c r="A3" s="147">
+      <c r="A3" s="145">
         <v>1</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="142" t="s">
-        <v>161</v>
+      <c r="C3" s="140" t="s">
+        <v>159</v>
       </c>
-      <c r="D3" s="311"/>
-      <c r="E3" s="312"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="177"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="175"/>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
-      <c r="K3" s="309"/>
-      <c r="L3" s="309"/>
-      <c r="M3" s="309"/>
-      <c r="N3" s="309"/>
-      <c r="O3" s="309"/>
-      <c r="P3" s="309"/>
-      <c r="Q3" s="309"/>
-      <c r="R3" s="309"/>
-      <c r="S3" s="309"/>
-      <c r="T3" s="309"/>
-      <c r="U3" s="309"/>
-      <c r="V3" s="309"/>
-      <c r="W3" s="309"/>
-      <c r="X3" s="309"/>
-      <c r="Y3" s="309"/>
-      <c r="Z3" s="309"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="185"/>
+      <c r="P3" s="185"/>
+      <c r="Q3" s="185"/>
+      <c r="R3" s="185"/>
+      <c r="S3" s="185"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="185"/>
       <c r="AA3" s="32"/>
       <c r="AB3" s="32"/>
       <c r="AC3" s="32"/>
     </row>
     <row r="4" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A4" s="147">
+      <c r="A4" s="145">
         <v>2</v>
       </c>
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="149"/>
-      <c r="D4" s="311"/>
-      <c r="E4" s="312"/>
-      <c r="F4" s="312"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="320"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="308"/>
-      <c r="J4" s="177"/>
-      <c r="K4" s="309"/>
-      <c r="L4" s="309"/>
-      <c r="M4" s="309"/>
-      <c r="N4" s="309"/>
-      <c r="O4" s="309"/>
-      <c r="P4" s="309"/>
-      <c r="Q4" s="309"/>
-      <c r="R4" s="309"/>
-      <c r="S4" s="309"/>
-      <c r="T4" s="309"/>
-      <c r="U4" s="309"/>
-      <c r="V4" s="309"/>
-      <c r="W4" s="309"/>
-      <c r="X4" s="309"/>
-      <c r="Y4" s="309"/>
-      <c r="Z4" s="309"/>
+      <c r="I4" s="185"/>
+      <c r="J4" s="175"/>
+      <c r="K4" s="185"/>
+      <c r="L4" s="185"/>
+      <c r="M4" s="185"/>
+      <c r="N4" s="185"/>
+      <c r="O4" s="185"/>
+      <c r="P4" s="185"/>
+      <c r="Q4" s="185"/>
+      <c r="R4" s="185"/>
+      <c r="S4" s="185"/>
+      <c r="T4" s="185"/>
+      <c r="U4" s="185"/>
+      <c r="V4" s="185"/>
+      <c r="W4" s="185"/>
+      <c r="X4" s="185"/>
+      <c r="Y4" s="185"/>
+      <c r="Z4" s="185"/>
       <c r="AA4" s="32"/>
       <c r="AB4" s="32"/>
       <c r="AC4" s="32"/>
     </row>
     <row r="5" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A5" s="150">
+      <c r="A5" s="148">
         <v>43467</v>
       </c>
-      <c r="B5" s="306" t="s">
-        <v>194</v>
+      <c r="B5" s="183" t="s">
+        <v>192</v>
       </c>
-      <c r="C5" s="142" t="str">
+      <c r="C5" s="140" t="str">
         <f>Appendix!C48</f>
         <v>Đỗ Việt Cường - 21130299</v>
       </c>
-      <c r="D5" s="313"/>
-      <c r="E5" s="314"/>
-      <c r="F5" s="314"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="309"/>
+      <c r="F5" s="309"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="308"/>
-      <c r="J5" s="308"/>
-      <c r="K5" s="308"/>
-      <c r="L5" s="309"/>
-      <c r="M5" s="309"/>
-      <c r="N5" s="309"/>
-      <c r="O5" s="309"/>
-      <c r="P5" s="309"/>
-      <c r="Q5" s="309"/>
-      <c r="R5" s="309"/>
-      <c r="S5" s="309"/>
-      <c r="T5" s="309"/>
-      <c r="U5" s="309"/>
-      <c r="V5" s="309"/>
-      <c r="W5" s="309"/>
-      <c r="X5" s="309"/>
-      <c r="Y5" s="309"/>
-      <c r="Z5" s="309"/>
+      <c r="I5" s="185"/>
+      <c r="J5" s="185"/>
+      <c r="K5" s="185"/>
+      <c r="L5" s="185"/>
+      <c r="M5" s="185"/>
+      <c r="N5" s="185"/>
+      <c r="O5" s="185"/>
+      <c r="P5" s="185"/>
+      <c r="Q5" s="185"/>
+      <c r="R5" s="185"/>
+      <c r="S5" s="185"/>
+      <c r="T5" s="185"/>
+      <c r="U5" s="185"/>
+      <c r="V5" s="185"/>
+      <c r="W5" s="185"/>
+      <c r="X5" s="185"/>
+      <c r="Y5" s="185"/>
+      <c r="Z5" s="185"/>
       <c r="AA5" s="32"/>
       <c r="AB5" s="32"/>
       <c r="AC5" s="32"/>
     </row>
     <row r="6" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A6" s="150">
+      <c r="A6" s="148">
         <v>43498</v>
       </c>
-      <c r="B6" s="306" t="s">
-        <v>195</v>
+      <c r="B6" s="183" t="s">
+        <v>193</v>
       </c>
-      <c r="C6" s="142" t="str">
+      <c r="C6" s="140" t="str">
         <f>Appendix!C49</f>
         <v>Lâm Trạch Đông - 21130317</v>
       </c>
-      <c r="D6" s="313"/>
-      <c r="E6" s="314"/>
-      <c r="F6" s="314"/>
+      <c r="D6" s="311"/>
+      <c r="E6" s="309"/>
+      <c r="F6" s="309"/>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="308"/>
-      <c r="J6" s="308"/>
-      <c r="K6" s="308"/>
-      <c r="L6" s="309"/>
-      <c r="M6" s="309"/>
-      <c r="N6" s="309"/>
-      <c r="O6" s="309"/>
-      <c r="P6" s="309"/>
-      <c r="Q6" s="309"/>
-      <c r="R6" s="309"/>
-      <c r="S6" s="309"/>
-      <c r="T6" s="309"/>
-      <c r="U6" s="309"/>
-      <c r="V6" s="309"/>
-      <c r="W6" s="309"/>
-      <c r="X6" s="309"/>
-      <c r="Y6" s="309"/>
-      <c r="Z6" s="309"/>
+      <c r="I6" s="185"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="185"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="185"/>
+      <c r="N6" s="185"/>
+      <c r="O6" s="185"/>
+      <c r="P6" s="185"/>
+      <c r="Q6" s="185"/>
+      <c r="R6" s="185"/>
+      <c r="S6" s="185"/>
+      <c r="T6" s="185"/>
+      <c r="U6" s="185"/>
+      <c r="V6" s="185"/>
+      <c r="W6" s="185"/>
+      <c r="X6" s="185"/>
+      <c r="Y6" s="185"/>
+      <c r="Z6" s="185"/>
       <c r="AA6" s="32"/>
       <c r="AB6" s="32"/>
       <c r="AC6" s="32"/>
     </row>
     <row r="7" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A7" s="150">
+      <c r="A7" s="148">
         <v>43526</v>
       </c>
-      <c r="B7" s="306" t="s">
-        <v>196</v>
+      <c r="B7" s="183" t="s">
+        <v>194</v>
       </c>
-      <c r="C7" s="142" t="str">
+      <c r="C7" s="140" t="str">
         <f>Appendix!C50</f>
         <v>Nguyễn Quốc Anh Tuấn - 21130601</v>
       </c>
-      <c r="D7" s="313"/>
-      <c r="E7" s="314"/>
+      <c r="D7" s="311"/>
+      <c r="E7" s="309"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="308"/>
-      <c r="J7" s="308"/>
-      <c r="K7" s="308"/>
-      <c r="L7" s="309"/>
-      <c r="M7" s="309"/>
-      <c r="N7" s="309"/>
-      <c r="O7" s="309"/>
-      <c r="P7" s="309"/>
-      <c r="Q7" s="309"/>
-      <c r="R7" s="309"/>
-      <c r="S7" s="309"/>
-      <c r="T7" s="309"/>
-      <c r="U7" s="309"/>
-      <c r="V7" s="309"/>
-      <c r="W7" s="309"/>
-      <c r="X7" s="309"/>
-      <c r="Y7" s="309"/>
-      <c r="Z7" s="309"/>
+      <c r="I7" s="185"/>
+      <c r="J7" s="185"/>
+      <c r="K7" s="185"/>
+      <c r="L7" s="185"/>
+      <c r="M7" s="185"/>
+      <c r="N7" s="185"/>
+      <c r="O7" s="185"/>
+      <c r="P7" s="185"/>
+      <c r="Q7" s="185"/>
+      <c r="R7" s="185"/>
+      <c r="S7" s="185"/>
+      <c r="T7" s="185"/>
+      <c r="U7" s="185"/>
+      <c r="V7" s="185"/>
+      <c r="W7" s="185"/>
+      <c r="X7" s="185"/>
+      <c r="Y7" s="185"/>
+      <c r="Z7" s="185"/>
       <c r="AA7" s="32"/>
       <c r="AB7" s="32"/>
       <c r="AC7" s="32"/>
     </row>
     <row r="8" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A8" s="150">
+      <c r="A8" s="148">
         <v>43557</v>
       </c>
-      <c r="B8" s="306" t="s">
-        <v>197</v>
+      <c r="B8" s="183" t="s">
+        <v>195</v>
       </c>
-      <c r="C8" s="142" t="str">
+      <c r="C8" s="140" t="str">
         <f>Appendix!C51</f>
         <v>Phạm Nhựt Tân - 21130530</v>
       </c>
-      <c r="D8" s="313"/>
-      <c r="E8" s="314"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
-      <c r="I8" s="308"/>
-      <c r="J8" s="308"/>
-      <c r="K8" s="308"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="309"/>
-      <c r="N8" s="309"/>
-      <c r="O8" s="309"/>
-      <c r="P8" s="309"/>
-      <c r="Q8" s="309"/>
-      <c r="R8" s="309"/>
-      <c r="S8" s="309"/>
-      <c r="T8" s="309"/>
-      <c r="U8" s="309"/>
-      <c r="V8" s="309"/>
-      <c r="W8" s="309"/>
-      <c r="X8" s="309"/>
-      <c r="Y8" s="309"/>
-      <c r="Z8" s="309"/>
+      <c r="D8" s="311"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="150"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="185"/>
+      <c r="J8" s="185"/>
+      <c r="K8" s="185"/>
+      <c r="L8" s="185"/>
+      <c r="M8" s="185"/>
+      <c r="N8" s="185"/>
+      <c r="O8" s="185"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="185"/>
+      <c r="R8" s="185"/>
+      <c r="S8" s="185"/>
+      <c r="T8" s="185"/>
+      <c r="U8" s="185"/>
+      <c r="V8" s="185"/>
+      <c r="W8" s="185"/>
+      <c r="X8" s="185"/>
+      <c r="Y8" s="185"/>
+      <c r="Z8" s="185"/>
       <c r="AA8" s="32"/>
       <c r="AB8" s="32"/>
       <c r="AC8" s="32"/>
     </row>
     <row r="9" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A9" s="150">
+      <c r="A9" s="148">
         <v>43587</v>
       </c>
-      <c r="B9" s="306" t="s">
-        <v>198</v>
+      <c r="B9" s="183" t="s">
+        <v>196</v>
       </c>
-      <c r="C9" s="142" t="str">
+      <c r="C9" s="140" t="str">
         <f>Appendix!C52</f>
         <v>Trần Văn Triều - 21130639</v>
       </c>
-      <c r="D9" s="313"/>
-      <c r="E9" s="314"/>
+      <c r="D9" s="311"/>
+      <c r="E9" s="309"/>
       <c r="F9" s="37"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="308"/>
-      <c r="J9" s="308"/>
-      <c r="K9" s="308"/>
-      <c r="L9" s="309"/>
-      <c r="M9" s="309"/>
-      <c r="N9" s="309"/>
-      <c r="O9" s="309"/>
-      <c r="P9" s="309"/>
-      <c r="Q9" s="309"/>
-      <c r="R9" s="309"/>
-      <c r="S9" s="309"/>
-      <c r="T9" s="309"/>
-      <c r="U9" s="309"/>
-      <c r="V9" s="309"/>
-      <c r="W9" s="309"/>
-      <c r="X9" s="309"/>
-      <c r="Y9" s="309"/>
-      <c r="Z9" s="309"/>
+      <c r="I9" s="185"/>
+      <c r="J9" s="185"/>
+      <c r="K9" s="185"/>
+      <c r="L9" s="185"/>
+      <c r="M9" s="185"/>
+      <c r="N9" s="185"/>
+      <c r="O9" s="185"/>
+      <c r="P9" s="185"/>
+      <c r="Q9" s="185"/>
+      <c r="R9" s="185"/>
+      <c r="S9" s="185"/>
+      <c r="T9" s="185"/>
+      <c r="U9" s="185"/>
+      <c r="V9" s="185"/>
+      <c r="W9" s="185"/>
+      <c r="X9" s="185"/>
+      <c r="Y9" s="185"/>
+      <c r="Z9" s="185"/>
       <c r="AA9" s="32"/>
       <c r="AB9" s="32"/>
       <c r="AC9" s="32"/>
     </row>
     <row r="10" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A10" s="150">
+      <c r="A10" s="148">
         <v>43771</v>
       </c>
-      <c r="B10" s="151" t="s">
-        <v>162</v>
+      <c r="B10" s="149" t="s">
+        <v>160</v>
       </c>
-      <c r="C10" s="142" t="s">
-        <v>161</v>
+      <c r="C10" s="140" t="s">
+        <v>159</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
-      <c r="F10" s="178"/>
+      <c r="F10" s="176"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="308"/>
-      <c r="J10" s="308"/>
-      <c r="K10" s="308"/>
-      <c r="L10" s="309"/>
-      <c r="M10" s="309"/>
-      <c r="N10" s="309"/>
-      <c r="O10" s="309"/>
-      <c r="P10" s="309"/>
-      <c r="Q10" s="309"/>
-      <c r="R10" s="309"/>
-      <c r="S10" s="309"/>
-      <c r="T10" s="309"/>
-      <c r="U10" s="309"/>
-      <c r="V10" s="309"/>
-      <c r="W10" s="309"/>
-      <c r="X10" s="309"/>
-      <c r="Y10" s="309"/>
-      <c r="Z10" s="309"/>
+      <c r="I10" s="185"/>
+      <c r="J10" s="185"/>
+      <c r="K10" s="185"/>
+      <c r="L10" s="185"/>
+      <c r="M10" s="185"/>
+      <c r="N10" s="185"/>
+      <c r="O10" s="185"/>
+      <c r="P10" s="185"/>
+      <c r="Q10" s="185"/>
+      <c r="R10" s="185"/>
+      <c r="S10" s="185"/>
+      <c r="T10" s="185"/>
+      <c r="U10" s="185"/>
+      <c r="V10" s="185"/>
+      <c r="W10" s="185"/>
+      <c r="X10" s="185"/>
+      <c r="Y10" s="185"/>
+      <c r="Z10" s="185"/>
       <c r="AA10" s="32"/>
       <c r="AB10" s="32"/>
       <c r="AC10" s="32"/>
     </row>
     <row r="11" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A11" s="147">
+      <c r="A11" s="145">
         <v>3</v>
       </c>
-      <c r="B11" s="148" t="s">
-        <v>153</v>
+      <c r="B11" s="146" t="s">
+        <v>151</v>
       </c>
-      <c r="C11" s="153"/>
+      <c r="C11" s="151"/>
       <c r="E11" s="310"/>
       <c r="F11" s="310"/>
       <c r="G11" s="310"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="309"/>
-      <c r="L11" s="309"/>
-      <c r="M11" s="309"/>
-      <c r="N11" s="309"/>
-      <c r="O11" s="309"/>
-      <c r="P11" s="309"/>
-      <c r="Q11" s="309"/>
-      <c r="R11" s="309"/>
-      <c r="S11" s="309"/>
-      <c r="T11" s="309"/>
-      <c r="U11" s="309"/>
-      <c r="V11" s="309"/>
-      <c r="W11" s="309"/>
-      <c r="X11" s="309"/>
-      <c r="Y11" s="309"/>
-      <c r="Z11" s="309"/>
+      <c r="K11" s="185"/>
+      <c r="L11" s="185"/>
+      <c r="M11" s="185"/>
+      <c r="N11" s="185"/>
+      <c r="O11" s="185"/>
+      <c r="P11" s="185"/>
+      <c r="Q11" s="185"/>
+      <c r="R11" s="185"/>
+      <c r="S11" s="185"/>
+      <c r="T11" s="185"/>
+      <c r="U11" s="185"/>
+      <c r="V11" s="185"/>
+      <c r="W11" s="185"/>
+      <c r="X11" s="185"/>
+      <c r="Y11" s="185"/>
+      <c r="Z11" s="185"/>
       <c r="AA11" s="32"/>
       <c r="AB11" s="32"/>
       <c r="AC11" s="32"/>
     </row>
     <row r="12" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A12" s="150">
+      <c r="A12" s="148">
         <v>43468</v>
       </c>
-      <c r="B12" s="306" t="s">
-        <v>194</v>
+      <c r="B12" s="183" t="s">
+        <v>192</v>
       </c>
-      <c r="C12" s="142" t="str">
+      <c r="C12" s="140" t="str">
         <f>Appendix!C48</f>
         <v>Đỗ Việt Cường - 21130299</v>
       </c>
       <c r="D12" s="32"/>
-      <c r="E12" s="314"/>
-      <c r="F12" s="314"/>
-      <c r="G12" s="314"/>
+      <c r="E12" s="309"/>
+      <c r="F12" s="309"/>
+      <c r="G12" s="309"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
-      <c r="J12" s="309"/>
-      <c r="K12" s="309"/>
-      <c r="L12" s="309"/>
-      <c r="M12" s="309"/>
-      <c r="N12" s="309"/>
-      <c r="O12" s="309"/>
-      <c r="P12" s="309"/>
-      <c r="Q12" s="309"/>
-      <c r="R12" s="309"/>
-      <c r="S12" s="309"/>
-      <c r="T12" s="309"/>
-      <c r="U12" s="309"/>
-      <c r="V12" s="309"/>
-      <c r="W12" s="309"/>
-      <c r="X12" s="309"/>
-      <c r="Y12" s="309"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="185"/>
+      <c r="L12" s="185"/>
+      <c r="M12" s="185"/>
+      <c r="N12" s="185"/>
+      <c r="O12" s="185"/>
+      <c r="P12" s="185"/>
+      <c r="Q12" s="185"/>
+      <c r="R12" s="185"/>
+      <c r="S12" s="185"/>
+      <c r="T12" s="185"/>
+      <c r="U12" s="185"/>
+      <c r="V12" s="185"/>
+      <c r="W12" s="185"/>
+      <c r="X12" s="185"/>
+      <c r="Y12" s="185"/>
       <c r="Z12" s="32"/>
       <c r="AA12" s="32"/>
       <c r="AB12" s="32"/>
     </row>
     <row r="13" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A13" s="150">
+      <c r="A13" s="148">
         <v>43499</v>
       </c>
-      <c r="B13" s="306" t="s">
-        <v>195</v>
+      <c r="B13" s="183" t="s">
+        <v>193</v>
       </c>
-      <c r="C13" s="142" t="str">
+      <c r="C13" s="140" t="str">
         <f>Appendix!C49</f>
         <v>Lâm Trạch Đông - 21130317</v>
       </c>
       <c r="D13" s="32"/>
-      <c r="E13" s="314"/>
-      <c r="F13" s="314"/>
-      <c r="G13" s="314"/>
+      <c r="E13" s="309"/>
+      <c r="F13" s="309"/>
+      <c r="G13" s="309"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
-      <c r="J13" s="309"/>
-      <c r="K13" s="309"/>
-      <c r="L13" s="309"/>
-      <c r="M13" s="309"/>
-      <c r="N13" s="309"/>
-      <c r="O13" s="309"/>
-      <c r="P13" s="309"/>
-      <c r="Q13" s="309"/>
-      <c r="R13" s="309"/>
-      <c r="S13" s="309"/>
-      <c r="T13" s="309"/>
-      <c r="U13" s="309"/>
-      <c r="V13" s="309"/>
-      <c r="W13" s="309"/>
-      <c r="X13" s="309"/>
-      <c r="Y13" s="309"/>
+      <c r="J13" s="185"/>
+      <c r="K13" s="185"/>
+      <c r="L13" s="185"/>
+      <c r="M13" s="185"/>
+      <c r="N13" s="185"/>
+      <c r="O13" s="185"/>
+      <c r="P13" s="185"/>
+      <c r="Q13" s="185"/>
+      <c r="R13" s="185"/>
+      <c r="S13" s="185"/>
+      <c r="T13" s="185"/>
+      <c r="U13" s="185"/>
+      <c r="V13" s="185"/>
+      <c r="W13" s="185"/>
+      <c r="X13" s="185"/>
+      <c r="Y13" s="185"/>
       <c r="Z13" s="32"/>
       <c r="AA13" s="32"/>
       <c r="AB13" s="32"/>
     </row>
     <row r="14" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A14" s="150">
+      <c r="A14" s="148">
         <v>43527</v>
       </c>
-      <c r="B14" s="306" t="s">
-        <v>196</v>
+      <c r="B14" s="183" t="s">
+        <v>194</v>
       </c>
-      <c r="C14" s="142" t="str">
+      <c r="C14" s="140" t="str">
         <f>Appendix!C50</f>
         <v>Nguyễn Quốc Anh Tuấn - 21130601</v>
       </c>
       <c r="D14" s="32"/>
-      <c r="E14" s="314"/>
-      <c r="F14" s="314"/>
-      <c r="G14" s="314"/>
+      <c r="E14" s="309"/>
+      <c r="F14" s="309"/>
+      <c r="G14" s="309"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="309"/>
-      <c r="L14" s="309"/>
-      <c r="M14" s="309"/>
-      <c r="N14" s="309"/>
-      <c r="O14" s="309"/>
-      <c r="P14" s="309"/>
-      <c r="Q14" s="309"/>
-      <c r="R14" s="309"/>
-      <c r="S14" s="309"/>
-      <c r="T14" s="309"/>
-      <c r="U14" s="309"/>
-      <c r="V14" s="309"/>
-      <c r="W14" s="309"/>
-      <c r="X14" s="309"/>
-      <c r="Y14" s="309"/>
-      <c r="Z14" s="309"/>
+      <c r="K14" s="185"/>
+      <c r="L14" s="185"/>
+      <c r="M14" s="185"/>
+      <c r="N14" s="185"/>
+      <c r="O14" s="185"/>
+      <c r="P14" s="185"/>
+      <c r="Q14" s="185"/>
+      <c r="R14" s="185"/>
+      <c r="S14" s="185"/>
+      <c r="T14" s="185"/>
+      <c r="U14" s="185"/>
+      <c r="V14" s="185"/>
+      <c r="W14" s="185"/>
+      <c r="X14" s="185"/>
+      <c r="Y14" s="185"/>
+      <c r="Z14" s="185"/>
       <c r="AA14" s="32"/>
       <c r="AB14" s="32"/>
       <c r="AC14" s="32"/>
     </row>
     <row r="15" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A15" s="150">
+      <c r="A15" s="148">
         <v>43558</v>
       </c>
-      <c r="B15" s="306" t="s">
-        <v>197</v>
+      <c r="B15" s="183" t="s">
+        <v>195</v>
       </c>
-      <c r="C15" s="142" t="str">
+      <c r="C15" s="140" t="str">
         <f>Appendix!C51</f>
         <v>Phạm Nhựt Tân - 21130530</v>
       </c>
       <c r="D15" s="32"/>
-      <c r="E15" s="314"/>
-      <c r="F15" s="314"/>
-      <c r="G15" s="314"/>
+      <c r="E15" s="309"/>
+      <c r="F15" s="309"/>
+      <c r="G15" s="309"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
-      <c r="K15" s="309"/>
-      <c r="L15" s="309"/>
-      <c r="M15" s="309"/>
-      <c r="N15" s="309"/>
-      <c r="O15" s="309"/>
-      <c r="P15" s="309"/>
-      <c r="Q15" s="309"/>
-      <c r="R15" s="309"/>
-      <c r="S15" s="309"/>
-      <c r="T15" s="309"/>
-      <c r="U15" s="309"/>
-      <c r="V15" s="309"/>
-      <c r="W15" s="309"/>
-      <c r="X15" s="309"/>
-      <c r="Y15" s="309"/>
-      <c r="Z15" s="309"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="185"/>
+      <c r="N15" s="185"/>
+      <c r="O15" s="185"/>
+      <c r="P15" s="185"/>
+      <c r="Q15" s="185"/>
+      <c r="R15" s="185"/>
+      <c r="S15" s="185"/>
+      <c r="T15" s="185"/>
+      <c r="U15" s="185"/>
+      <c r="V15" s="185"/>
+      <c r="W15" s="185"/>
+      <c r="X15" s="185"/>
+      <c r="Y15" s="185"/>
+      <c r="Z15" s="185"/>
       <c r="AA15" s="32"/>
       <c r="AB15" s="32"/>
       <c r="AC15" s="32"/>
     </row>
     <row r="16" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A16" s="150">
+      <c r="A16" s="148">
         <v>43588</v>
       </c>
-      <c r="B16" s="306" t="s">
-        <v>198</v>
+      <c r="B16" s="183" t="s">
+        <v>196</v>
       </c>
-      <c r="C16" s="142" t="str">
+      <c r="C16" s="140" t="str">
         <f>Appendix!C52</f>
         <v>Trần Văn Triều - 21130639</v>
       </c>
       <c r="D16" s="32"/>
-      <c r="E16" s="314"/>
-      <c r="F16" s="314"/>
-      <c r="G16" s="314"/>
+      <c r="E16" s="309"/>
+      <c r="F16" s="309"/>
+      <c r="G16" s="309"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
-      <c r="K16" s="309"/>
-      <c r="L16" s="309"/>
-      <c r="M16" s="309"/>
-      <c r="N16" s="309"/>
-      <c r="O16" s="309"/>
-      <c r="P16" s="309"/>
-      <c r="Q16" s="309"/>
-      <c r="R16" s="309"/>
-      <c r="S16" s="309"/>
-      <c r="T16" s="309"/>
-      <c r="U16" s="309"/>
-      <c r="V16" s="309"/>
-      <c r="W16" s="309"/>
-      <c r="X16" s="309"/>
-      <c r="Y16" s="309"/>
-      <c r="Z16" s="309"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="185"/>
+      <c r="M16" s="185"/>
+      <c r="N16" s="185"/>
+      <c r="O16" s="185"/>
+      <c r="P16" s="185"/>
+      <c r="Q16" s="185"/>
+      <c r="R16" s="185"/>
+      <c r="S16" s="185"/>
+      <c r="T16" s="185"/>
+      <c r="U16" s="185"/>
+      <c r="V16" s="185"/>
+      <c r="W16" s="185"/>
+      <c r="X16" s="185"/>
+      <c r="Y16" s="185"/>
+      <c r="Z16" s="185"/>
       <c r="AA16" s="32"/>
       <c r="AB16" s="32"/>
       <c r="AC16" s="32"/>
     </row>
     <row r="17" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A17" s="150">
+      <c r="A17" s="148">
         <v>43772</v>
       </c>
-      <c r="B17" s="151" t="s">
-        <v>162</v>
+      <c r="B17" s="149" t="s">
+        <v>160</v>
       </c>
-      <c r="C17" s="142" t="s">
-        <v>161</v>
+      <c r="C17" s="140" t="s">
+        <v>159</v>
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="178"/>
+      <c r="G17" s="176"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
-      <c r="K17" s="309"/>
-      <c r="L17" s="309"/>
-      <c r="M17" s="309"/>
-      <c r="N17" s="309"/>
-      <c r="O17" s="309"/>
-      <c r="P17" s="309"/>
-      <c r="Q17" s="309"/>
-      <c r="R17" s="309"/>
-      <c r="S17" s="309"/>
-      <c r="T17" s="309"/>
-      <c r="U17" s="309"/>
-      <c r="V17" s="309"/>
-      <c r="W17" s="309"/>
-      <c r="X17" s="309"/>
-      <c r="Y17" s="309"/>
-      <c r="Z17" s="309"/>
+      <c r="K17" s="185"/>
+      <c r="L17" s="185"/>
+      <c r="M17" s="185"/>
+      <c r="N17" s="185"/>
+      <c r="O17" s="185"/>
+      <c r="P17" s="185"/>
+      <c r="Q17" s="185"/>
+      <c r="R17" s="185"/>
+      <c r="S17" s="185"/>
+      <c r="T17" s="185"/>
+      <c r="U17" s="185"/>
+      <c r="V17" s="185"/>
+      <c r="W17" s="185"/>
+      <c r="X17" s="185"/>
+      <c r="Y17" s="185"/>
+      <c r="Z17" s="185"/>
       <c r="AA17" s="32"/>
       <c r="AB17" s="32"/>
       <c r="AC17" s="32"/>
     </row>
     <row r="18" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A18" s="147">
+      <c r="A18" s="145">
         <v>4</v>
       </c>
-      <c r="B18" s="153" t="s">
-        <v>163</v>
+      <c r="B18" s="151" t="s">
+        <v>161</v>
       </c>
-      <c r="C18" s="154"/>
+      <c r="C18" s="152"/>
       <c r="D18" s="32"/>
       <c r="E18" s="310"/>
       <c r="F18" s="310"/>
@@ -42528,329 +42548,329 @@
       <c r="H18" s="310"/>
       <c r="I18" s="310"/>
       <c r="J18" s="32"/>
-      <c r="K18" s="309"/>
-      <c r="L18" s="309"/>
-      <c r="M18" s="309"/>
-      <c r="N18" s="309"/>
-      <c r="O18" s="309"/>
-      <c r="P18" s="309"/>
-      <c r="Q18" s="309"/>
-      <c r="R18" s="309"/>
-      <c r="S18" s="309"/>
-      <c r="T18" s="309"/>
-      <c r="U18" s="309"/>
-      <c r="V18" s="309"/>
-      <c r="W18" s="309"/>
-      <c r="X18" s="309"/>
-      <c r="Y18" s="309"/>
-      <c r="Z18" s="309"/>
+      <c r="K18" s="185"/>
+      <c r="L18" s="185"/>
+      <c r="M18" s="185"/>
+      <c r="N18" s="185"/>
+      <c r="O18" s="185"/>
+      <c r="P18" s="185"/>
+      <c r="Q18" s="185"/>
+      <c r="R18" s="185"/>
+      <c r="S18" s="185"/>
+      <c r="T18" s="185"/>
+      <c r="U18" s="185"/>
+      <c r="V18" s="185"/>
+      <c r="W18" s="185"/>
+      <c r="X18" s="185"/>
+      <c r="Y18" s="185"/>
+      <c r="Z18" s="185"/>
       <c r="AA18" s="32"/>
       <c r="AB18" s="32"/>
       <c r="AC18" s="32"/>
     </row>
     <row r="19" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A19" s="150">
+      <c r="A19" s="148">
         <v>43469</v>
       </c>
-      <c r="B19" s="306" t="s">
-        <v>194</v>
+      <c r="B19" s="183" t="s">
+        <v>192</v>
       </c>
-      <c r="C19" s="142" t="str">
+      <c r="C19" s="140" t="str">
         <f>Appendix!C48</f>
         <v>Đỗ Việt Cường - 21130299</v>
       </c>
       <c r="D19" s="32"/>
-      <c r="E19" s="314"/>
-      <c r="F19" s="314"/>
-      <c r="G19" s="314"/>
-      <c r="H19" s="314"/>
+      <c r="E19" s="309"/>
+      <c r="F19" s="309"/>
+      <c r="G19" s="309"/>
+      <c r="H19" s="309"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
-      <c r="K19" s="309"/>
-      <c r="L19" s="309"/>
-      <c r="M19" s="309"/>
-      <c r="N19" s="309"/>
-      <c r="O19" s="309"/>
-      <c r="P19" s="309"/>
-      <c r="Q19" s="309"/>
-      <c r="R19" s="309"/>
-      <c r="S19" s="309"/>
-      <c r="T19" s="309"/>
-      <c r="U19" s="309"/>
-      <c r="V19" s="309"/>
-      <c r="W19" s="309"/>
-      <c r="X19" s="309"/>
-      <c r="Y19" s="309"/>
-      <c r="Z19" s="309"/>
+      <c r="K19" s="185"/>
+      <c r="L19" s="185"/>
+      <c r="M19" s="185"/>
+      <c r="N19" s="185"/>
+      <c r="O19" s="185"/>
+      <c r="P19" s="185"/>
+      <c r="Q19" s="185"/>
+      <c r="R19" s="185"/>
+      <c r="S19" s="185"/>
+      <c r="T19" s="185"/>
+      <c r="U19" s="185"/>
+      <c r="V19" s="185"/>
+      <c r="W19" s="185"/>
+      <c r="X19" s="185"/>
+      <c r="Y19" s="185"/>
+      <c r="Z19" s="185"/>
       <c r="AA19" s="32"/>
       <c r="AB19" s="32"/>
       <c r="AC19" s="32"/>
     </row>
     <row r="20" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A20" s="155">
+      <c r="A20" s="153">
         <v>43500</v>
       </c>
-      <c r="B20" s="306" t="s">
-        <v>195</v>
+      <c r="B20" s="183" t="s">
+        <v>193</v>
       </c>
-      <c r="C20" s="142" t="str">
+      <c r="C20" s="140" t="str">
         <f>Appendix!C49</f>
         <v>Lâm Trạch Đông - 21130317</v>
       </c>
       <c r="D20" s="32"/>
-      <c r="E20" s="314"/>
-      <c r="F20" s="314"/>
-      <c r="G20" s="314"/>
-      <c r="H20" s="314"/>
+      <c r="E20" s="309"/>
+      <c r="F20" s="309"/>
+      <c r="G20" s="309"/>
+      <c r="H20" s="309"/>
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
-      <c r="K20" s="309"/>
-      <c r="L20" s="309"/>
-      <c r="M20" s="309"/>
-      <c r="N20" s="309"/>
-      <c r="O20" s="309"/>
-      <c r="P20" s="309"/>
-      <c r="Q20" s="309"/>
-      <c r="R20" s="309"/>
-      <c r="S20" s="309"/>
-      <c r="T20" s="309"/>
-      <c r="U20" s="309"/>
-      <c r="V20" s="309"/>
-      <c r="W20" s="309"/>
-      <c r="X20" s="309"/>
-      <c r="Y20" s="309"/>
-      <c r="Z20" s="309"/>
+      <c r="K20" s="185"/>
+      <c r="L20" s="185"/>
+      <c r="M20" s="185"/>
+      <c r="N20" s="185"/>
+      <c r="O20" s="185"/>
+      <c r="P20" s="185"/>
+      <c r="Q20" s="185"/>
+      <c r="R20" s="185"/>
+      <c r="S20" s="185"/>
+      <c r="T20" s="185"/>
+      <c r="U20" s="185"/>
+      <c r="V20" s="185"/>
+      <c r="W20" s="185"/>
+      <c r="X20" s="185"/>
+      <c r="Y20" s="185"/>
+      <c r="Z20" s="185"/>
       <c r="AA20" s="32"/>
       <c r="AB20" s="32"/>
       <c r="AC20" s="32"/>
     </row>
     <row r="21" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A21" s="155">
+      <c r="A21" s="153">
         <v>43528</v>
       </c>
-      <c r="B21" s="306" t="s">
-        <v>196</v>
+      <c r="B21" s="183" t="s">
+        <v>194</v>
       </c>
-      <c r="C21" s="142" t="str">
+      <c r="C21" s="140" t="str">
         <f>Appendix!C50</f>
         <v>Nguyễn Quốc Anh Tuấn - 21130601</v>
       </c>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
-      <c r="F21" s="314"/>
-      <c r="G21" s="314"/>
-      <c r="H21" s="314"/>
+      <c r="F21" s="309"/>
+      <c r="G21" s="309"/>
+      <c r="H21" s="309"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
-      <c r="K21" s="309"/>
-      <c r="L21" s="309"/>
-      <c r="M21" s="309"/>
-      <c r="N21" s="309"/>
-      <c r="O21" s="309"/>
-      <c r="P21" s="309"/>
-      <c r="Q21" s="309"/>
-      <c r="R21" s="309"/>
-      <c r="S21" s="309"/>
-      <c r="T21" s="309"/>
-      <c r="U21" s="309"/>
-      <c r="V21" s="309"/>
-      <c r="W21" s="309"/>
-      <c r="X21" s="309"/>
-      <c r="Y21" s="309"/>
-      <c r="Z21" s="309"/>
+      <c r="K21" s="185"/>
+      <c r="L21" s="185"/>
+      <c r="M21" s="185"/>
+      <c r="N21" s="185"/>
+      <c r="O21" s="185"/>
+      <c r="P21" s="185"/>
+      <c r="Q21" s="185"/>
+      <c r="R21" s="185"/>
+      <c r="S21" s="185"/>
+      <c r="T21" s="185"/>
+      <c r="U21" s="185"/>
+      <c r="V21" s="185"/>
+      <c r="W21" s="185"/>
+      <c r="X21" s="185"/>
+      <c r="Y21" s="185"/>
+      <c r="Z21" s="185"/>
       <c r="AA21" s="32"/>
       <c r="AB21" s="32"/>
       <c r="AC21" s="32"/>
     </row>
     <row r="22" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A22" s="155">
+      <c r="A22" s="153">
         <v>43559</v>
       </c>
-      <c r="B22" s="306" t="s">
-        <v>197</v>
+      <c r="B22" s="183" t="s">
+        <v>195</v>
       </c>
-      <c r="C22" s="142" t="str">
+      <c r="C22" s="140" t="str">
         <f>Appendix!C51</f>
         <v>Phạm Nhựt Tân - 21130530</v>
       </c>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
-      <c r="G22" s="314"/>
-      <c r="H22" s="314"/>
-      <c r="I22" s="314"/>
+      <c r="G22" s="309"/>
+      <c r="H22" s="309"/>
+      <c r="I22" s="309"/>
       <c r="J22" s="32"/>
-      <c r="K22" s="309"/>
-      <c r="L22" s="309"/>
-      <c r="M22" s="309"/>
-      <c r="N22" s="309"/>
-      <c r="O22" s="309"/>
-      <c r="P22" s="309"/>
-      <c r="Q22" s="309"/>
-      <c r="R22" s="309"/>
-      <c r="S22" s="309"/>
-      <c r="T22" s="309"/>
-      <c r="U22" s="309"/>
-      <c r="V22" s="309"/>
-      <c r="W22" s="309"/>
-      <c r="X22" s="309"/>
-      <c r="Y22" s="309"/>
-      <c r="Z22" s="309"/>
+      <c r="K22" s="185"/>
+      <c r="L22" s="185"/>
+      <c r="M22" s="185"/>
+      <c r="N22" s="185"/>
+      <c r="O22" s="185"/>
+      <c r="P22" s="185"/>
+      <c r="Q22" s="185"/>
+      <c r="R22" s="185"/>
+      <c r="S22" s="185"/>
+      <c r="T22" s="185"/>
+      <c r="U22" s="185"/>
+      <c r="V22" s="185"/>
+      <c r="W22" s="185"/>
+      <c r="X22" s="185"/>
+      <c r="Y22" s="185"/>
+      <c r="Z22" s="185"/>
       <c r="AA22" s="32"/>
       <c r="AB22" s="32"/>
       <c r="AC22" s="32"/>
     </row>
     <row r="23" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A23" s="155">
+      <c r="A23" s="153">
         <v>43589</v>
       </c>
-      <c r="B23" s="306" t="s">
-        <v>198</v>
+      <c r="B23" s="183" t="s">
+        <v>196</v>
       </c>
-      <c r="C23" s="142" t="str">
+      <c r="C23" s="140" t="str">
         <f>Appendix!C52</f>
         <v>Trần Văn Triều - 21130639</v>
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
-      <c r="G23" s="314"/>
-      <c r="H23" s="314"/>
-      <c r="I23" s="314"/>
+      <c r="G23" s="309"/>
+      <c r="H23" s="309"/>
+      <c r="I23" s="309"/>
       <c r="J23" s="32"/>
-      <c r="K23" s="309"/>
-      <c r="L23" s="309"/>
-      <c r="M23" s="309"/>
-      <c r="N23" s="309"/>
-      <c r="O23" s="309"/>
-      <c r="P23" s="309"/>
-      <c r="Q23" s="309"/>
-      <c r="R23" s="309"/>
-      <c r="S23" s="309"/>
-      <c r="T23" s="309"/>
-      <c r="U23" s="309"/>
-      <c r="V23" s="309"/>
-      <c r="W23" s="309"/>
-      <c r="X23" s="309"/>
-      <c r="Y23" s="309"/>
-      <c r="Z23" s="309"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="185"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="185"/>
+      <c r="P23" s="185"/>
+      <c r="Q23" s="185"/>
+      <c r="R23" s="185"/>
+      <c r="S23" s="185"/>
+      <c r="T23" s="185"/>
+      <c r="U23" s="185"/>
+      <c r="V23" s="185"/>
+      <c r="W23" s="185"/>
+      <c r="X23" s="185"/>
+      <c r="Y23" s="185"/>
+      <c r="Z23" s="185"/>
       <c r="AA23" s="32"/>
       <c r="AB23" s="32"/>
       <c r="AC23" s="32"/>
     </row>
     <row r="24" spans="1:29" ht="12.75" customHeight="1" outlineLevel="1">
-      <c r="A24" s="150">
+      <c r="A24" s="148">
         <v>43773</v>
       </c>
-      <c r="B24" s="151" t="s">
-        <v>162</v>
+      <c r="B24" s="149" t="s">
+        <v>160</v>
       </c>
-      <c r="C24" s="142" t="s">
-        <v>161</v>
+      <c r="C24" s="140" t="s">
+        <v>159</v>
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
-      <c r="I24" s="178"/>
+      <c r="I24" s="176"/>
       <c r="J24" s="32"/>
-      <c r="K24" s="309"/>
-      <c r="L24" s="309"/>
-      <c r="M24" s="309"/>
-      <c r="N24" s="309"/>
-      <c r="O24" s="309"/>
-      <c r="P24" s="309"/>
-      <c r="Q24" s="309"/>
-      <c r="R24" s="309"/>
-      <c r="S24" s="309"/>
-      <c r="T24" s="309"/>
-      <c r="U24" s="309"/>
-      <c r="V24" s="309"/>
-      <c r="W24" s="309"/>
-      <c r="X24" s="309"/>
-      <c r="Y24" s="309"/>
-      <c r="Z24" s="309"/>
+      <c r="K24" s="185"/>
+      <c r="L24" s="185"/>
+      <c r="M24" s="185"/>
+      <c r="N24" s="185"/>
+      <c r="O24" s="185"/>
+      <c r="P24" s="185"/>
+      <c r="Q24" s="185"/>
+      <c r="R24" s="185"/>
+      <c r="S24" s="185"/>
+      <c r="T24" s="185"/>
+      <c r="U24" s="185"/>
+      <c r="V24" s="185"/>
+      <c r="W24" s="185"/>
+      <c r="X24" s="185"/>
+      <c r="Y24" s="185"/>
+      <c r="Z24" s="185"/>
       <c r="AA24" s="32"/>
       <c r="AB24" s="32"/>
       <c r="AC24" s="32"/>
     </row>
     <row r="25" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A25" s="154">
+      <c r="A25" s="152">
         <v>5</v>
       </c>
-      <c r="B25" s="153" t="s">
-        <v>155</v>
+      <c r="B25" s="151" t="s">
+        <v>153</v>
       </c>
-      <c r="C25" s="143" t="s">
-        <v>161</v>
+      <c r="C25" s="141" t="s">
+        <v>159</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="32"/>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
-      <c r="I25" s="178"/>
-      <c r="J25" s="308"/>
-      <c r="K25" s="309"/>
-      <c r="L25" s="309"/>
-      <c r="M25" s="309"/>
-      <c r="N25" s="309"/>
-      <c r="O25" s="309"/>
-      <c r="P25" s="309"/>
-      <c r="Q25" s="309"/>
-      <c r="R25" s="309"/>
-      <c r="S25" s="309"/>
-      <c r="T25" s="309"/>
-      <c r="U25" s="309"/>
-      <c r="V25" s="309"/>
-      <c r="W25" s="309"/>
-      <c r="X25" s="309"/>
-      <c r="Y25" s="309"/>
-      <c r="Z25" s="309"/>
+      <c r="I25" s="176"/>
+      <c r="J25" s="185"/>
+      <c r="K25" s="185"/>
+      <c r="L25" s="185"/>
+      <c r="M25" s="185"/>
+      <c r="N25" s="185"/>
+      <c r="O25" s="185"/>
+      <c r="P25" s="185"/>
+      <c r="Q25" s="185"/>
+      <c r="R25" s="185"/>
+      <c r="S25" s="185"/>
+      <c r="T25" s="185"/>
+      <c r="U25" s="185"/>
+      <c r="V25" s="185"/>
+      <c r="W25" s="185"/>
+      <c r="X25" s="185"/>
+      <c r="Y25" s="185"/>
+      <c r="Z25" s="185"/>
       <c r="AA25" s="32"/>
       <c r="AB25" s="32"/>
       <c r="AC25" s="32"/>
     </row>
     <row r="26" spans="1:29" ht="15.75" customHeight="1">
-      <c r="A26" s="156">
+      <c r="A26" s="154">
         <v>6</v>
       </c>
-      <c r="B26" s="153" t="s">
-        <v>162</v>
+      <c r="B26" s="151" t="s">
+        <v>160</v>
       </c>
-      <c r="C26" s="157" t="s">
-        <v>161</v>
+      <c r="C26" s="155" t="s">
+        <v>159</v>
       </c>
-      <c r="J26" s="307" t="s">
-        <v>129</v>
+      <c r="J26" s="184" t="s">
+        <v>128</v>
       </c>
-      <c r="K26" s="309"/>
-      <c r="L26" s="309"/>
-      <c r="M26" s="309"/>
-      <c r="N26" s="309"/>
-      <c r="O26" s="309"/>
-      <c r="P26" s="309"/>
-      <c r="Q26" s="309"/>
-      <c r="R26" s="309"/>
-      <c r="S26" s="309"/>
-      <c r="T26" s="309"/>
-      <c r="U26" s="309"/>
-      <c r="V26" s="309"/>
-      <c r="W26" s="309"/>
-      <c r="X26" s="309"/>
-      <c r="Y26" s="309"/>
-      <c r="Z26" s="309"/>
+      <c r="K26" s="185"/>
+      <c r="L26" s="185"/>
+      <c r="M26" s="185"/>
+      <c r="N26" s="185"/>
+      <c r="O26" s="185"/>
+      <c r="P26" s="185"/>
+      <c r="Q26" s="185"/>
+      <c r="R26" s="185"/>
+      <c r="S26" s="185"/>
+      <c r="T26" s="185"/>
+      <c r="U26" s="185"/>
+      <c r="V26" s="185"/>
+      <c r="W26" s="185"/>
+      <c r="X26" s="185"/>
+      <c r="Y26" s="185"/>
+      <c r="Z26" s="185"/>
     </row>
     <row r="27" spans="1:29" ht="15.75" customHeight="1">
-      <c r="S27" s="308"/>
-      <c r="T27" s="308"/>
-      <c r="U27" s="308"/>
-      <c r="V27" s="308"/>
-      <c r="W27" s="308"/>
-      <c r="X27" s="308"/>
-      <c r="Y27" s="308"/>
-      <c r="Z27" s="308"/>
+      <c r="S27" s="185"/>
+      <c r="T27" s="185"/>
+      <c r="U27" s="185"/>
+      <c r="V27" s="185"/>
+      <c r="W27" s="185"/>
+      <c r="X27" s="185"/>
+      <c r="Y27" s="185"/>
+      <c r="Z27" s="185"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1"/>
     <row r="29" spans="1:29" ht="15.75" customHeight="1"/>
@@ -43812,11 +43832,18 @@
     <row r="985" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E19:H19"/>
@@ -43824,18 +43851,11 @@
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="E13:G13"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="J1:R1"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -43845,14 +43865,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:X1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" customWidth="1"/>
-    <col min="4" max="4" width="75.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="42.1640625" customWidth="1"/>
+    <col min="4" max="4" width="75.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
     <col min="7" max="24" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -43886,10 +43906,10 @@
       <c r="A2" s="27"/>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
-      <c r="D2" s="158" t="s">
+      <c r="D2" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="159"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
@@ -43912,9 +43932,9 @@
     </row>
     <row r="3" spans="1:24" ht="12.75" customHeight="1">
       <c r="A3" s="27"/>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
       <c r="E3" s="27"/>
       <c r="F3" s="27"/>
       <c r="G3" s="27"/>
@@ -43939,10 +43959,10 @@
     <row r="4" spans="1:24" ht="12.75" customHeight="1">
       <c r="A4" s="27"/>
       <c r="B4" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C4" s="35"/>
-      <c r="D4" s="160"/>
+      <c r="D4" s="158"/>
       <c r="E4" s="27"/>
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
@@ -43966,14 +43986,14 @@
     </row>
     <row r="5" spans="1:24" ht="16.5" customHeight="1">
       <c r="A5" s="27"/>
-      <c r="B5" s="161" t="s">
+      <c r="B5" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="161" t="s">
-        <v>165</v>
+      <c r="C5" s="159" t="s">
+        <v>163</v>
       </c>
-      <c r="D5" s="162" t="s">
-        <v>166</v>
+      <c r="D5" s="160" t="s">
+        <v>164</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
@@ -43998,10 +44018,10 @@
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1">
       <c r="A6" s="27"/>
-      <c r="B6" s="163">
+      <c r="B6" s="161">
         <v>1</v>
       </c>
-      <c r="C6" s="163"/>
+      <c r="C6" s="161"/>
       <c r="D6" s="44"/>
       <c r="E6" s="27"/>
       <c r="F6" s="27"/>
@@ -44026,11 +44046,11 @@
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1">
       <c r="A7" s="27"/>
-      <c r="B7" s="164">
+      <c r="B7" s="162">
         <v>2</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="27"/>
       <c r="F7" s="27"/>
       <c r="G7" s="27"/>
@@ -44054,11 +44074,11 @@
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1">
       <c r="A8" s="27"/>
-      <c r="B8" s="164">
+      <c r="B8" s="162">
         <v>3</v>
       </c>
-      <c r="C8" s="164"/>
-      <c r="D8" s="48"/>
+      <c r="C8" s="162"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="27"/>
       <c r="F8" s="27"/>
       <c r="G8" s="27"/>
@@ -44082,11 +44102,11 @@
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1">
       <c r="A9" s="27"/>
-      <c r="B9" s="164">
+      <c r="B9" s="162">
         <v>4</v>
       </c>
-      <c r="C9" s="164"/>
-      <c r="D9" s="48"/>
+      <c r="C9" s="162"/>
+      <c r="D9" s="47"/>
       <c r="E9" s="27"/>
       <c r="F9" s="27"/>
       <c r="G9" s="27"/>
@@ -44110,11 +44130,11 @@
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1">
       <c r="A10" s="27"/>
-      <c r="B10" s="164">
+      <c r="B10" s="162">
         <v>5</v>
       </c>
-      <c r="C10" s="164"/>
-      <c r="D10" s="48"/>
+      <c r="C10" s="162"/>
+      <c r="D10" s="47"/>
       <c r="E10" s="27"/>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
@@ -44138,11 +44158,11 @@
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1">
       <c r="A11" s="27"/>
-      <c r="B11" s="164">
+      <c r="B11" s="162">
         <v>6</v>
       </c>
-      <c r="C11" s="164"/>
-      <c r="D11" s="48"/>
+      <c r="C11" s="162"/>
+      <c r="D11" s="47"/>
       <c r="E11" s="27"/>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
@@ -44166,11 +44186,11 @@
     </row>
     <row r="12" spans="1:24" ht="14.25" customHeight="1">
       <c r="A12" s="27"/>
-      <c r="B12" s="164">
+      <c r="B12" s="162">
         <v>7</v>
       </c>
-      <c r="C12" s="164"/>
-      <c r="D12" s="48"/>
+      <c r="C12" s="162"/>
+      <c r="D12" s="47"/>
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
       <c r="G12" s="27"/>
@@ -44194,11 +44214,11 @@
     </row>
     <row r="13" spans="1:24" ht="14.25" customHeight="1">
       <c r="A13" s="27"/>
-      <c r="B13" s="164">
+      <c r="B13" s="162">
         <v>8</v>
       </c>
-      <c r="C13" s="164"/>
-      <c r="D13" s="48"/>
+      <c r="C13" s="162"/>
+      <c r="D13" s="47"/>
       <c r="E13" s="27"/>
       <c r="F13" s="27"/>
       <c r="G13" s="27"/>
@@ -44222,11 +44242,11 @@
     </row>
     <row r="14" spans="1:24" ht="14.25" customHeight="1">
       <c r="A14" s="27"/>
-      <c r="B14" s="164">
+      <c r="B14" s="162">
         <v>9</v>
       </c>
-      <c r="C14" s="164"/>
-      <c r="D14" s="48"/>
+      <c r="C14" s="162"/>
+      <c r="D14" s="47"/>
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
       <c r="G14" s="27"/>
@@ -44250,11 +44270,11 @@
     </row>
     <row r="15" spans="1:24" ht="14.25" customHeight="1">
       <c r="A15" s="27"/>
-      <c r="B15" s="164">
+      <c r="B15" s="162">
         <v>10</v>
       </c>
-      <c r="C15" s="164"/>
-      <c r="D15" s="48"/>
+      <c r="C15" s="162"/>
+      <c r="D15" s="47"/>
       <c r="E15" s="27"/>
       <c r="F15" s="27"/>
       <c r="G15" s="27"/>
@@ -44278,11 +44298,11 @@
     </row>
     <row r="16" spans="1:24" ht="14.25" customHeight="1">
       <c r="A16" s="27"/>
-      <c r="B16" s="164">
+      <c r="B16" s="162">
         <v>11</v>
       </c>
-      <c r="C16" s="164"/>
-      <c r="D16" s="48"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="47"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
@@ -44306,11 +44326,11 @@
     </row>
     <row r="17" spans="1:24" ht="14.25" customHeight="1">
       <c r="A17" s="27"/>
-      <c r="B17" s="164">
+      <c r="B17" s="162">
         <v>12</v>
       </c>
-      <c r="C17" s="164"/>
-      <c r="D17" s="48"/>
+      <c r="C17" s="162"/>
+      <c r="D17" s="47"/>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
@@ -44334,11 +44354,11 @@
     </row>
     <row r="18" spans="1:24" ht="14.25" customHeight="1">
       <c r="A18" s="27"/>
-      <c r="B18" s="164">
+      <c r="B18" s="162">
         <v>13</v>
       </c>
-      <c r="C18" s="164"/>
-      <c r="D18" s="48"/>
+      <c r="C18" s="162"/>
+      <c r="D18" s="47"/>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
       <c r="G18" s="27"/>
@@ -44362,11 +44382,11 @@
     </row>
     <row r="19" spans="1:24" ht="14.25" customHeight="1">
       <c r="A19" s="27"/>
-      <c r="B19" s="164">
+      <c r="B19" s="162">
         <v>14</v>
       </c>
-      <c r="C19" s="164"/>
-      <c r="D19" s="48"/>
+      <c r="C19" s="162"/>
+      <c r="D19" s="47"/>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
@@ -44390,11 +44410,11 @@
     </row>
     <row r="20" spans="1:24" ht="14.25" customHeight="1">
       <c r="A20" s="27"/>
-      <c r="B20" s="164">
+      <c r="B20" s="162">
         <v>15</v>
       </c>
-      <c r="C20" s="164"/>
-      <c r="D20" s="48"/>
+      <c r="C20" s="162"/>
+      <c r="D20" s="47"/>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
@@ -44418,11 +44438,11 @@
     </row>
     <row r="21" spans="1:24" ht="14.25" customHeight="1">
       <c r="A21" s="27"/>
-      <c r="B21" s="164">
+      <c r="B21" s="162">
         <v>17</v>
       </c>
-      <c r="C21" s="164"/>
-      <c r="D21" s="48"/>
+      <c r="C21" s="162"/>
+      <c r="D21" s="47"/>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
       <c r="G21" s="27"/>
@@ -44446,9 +44466,9 @@
     </row>
     <row r="22" spans="1:24" ht="12.75" customHeight="1">
       <c r="A22" s="27"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="166"/>
-      <c r="D22" s="167"/>
+      <c r="B22" s="163"/>
+      <c r="C22" s="164"/>
+      <c r="D22" s="165"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
       <c r="G22" s="27"/>
@@ -44525,7 +44545,7 @@
     <row r="25" spans="1:24" ht="12.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="35" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="35"/>
       <c r="D25" s="27"/>
@@ -44552,11 +44572,11 @@
     </row>
     <row r="26" spans="1:24" ht="12.75" customHeight="1">
       <c r="A26" s="27"/>
-      <c r="B26" s="162" t="s">
+      <c r="B26" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="162"/>
-      <c r="D26" s="162"/>
+      <c r="C26" s="160"/>
+      <c r="D26" s="160"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
@@ -44580,11 +44600,11 @@
     </row>
     <row r="27" spans="1:24" ht="12.75" customHeight="1">
       <c r="A27" s="27"/>
-      <c r="B27" s="168">
+      <c r="B27" s="166">
         <v>1</v>
       </c>
-      <c r="C27" s="164"/>
-      <c r="D27" s="48"/>
+      <c r="C27" s="162"/>
+      <c r="D27" s="47"/>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
@@ -44608,11 +44628,11 @@
     </row>
     <row r="28" spans="1:24" ht="12.75" customHeight="1">
       <c r="A28" s="27"/>
-      <c r="B28" s="168">
+      <c r="B28" s="166">
         <v>1</v>
       </c>
-      <c r="C28" s="164"/>
-      <c r="D28" s="48"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="47"/>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
@@ -44636,11 +44656,11 @@
     </row>
     <row r="29" spans="1:24" ht="69.75" customHeight="1">
       <c r="A29" s="27"/>
-      <c r="B29" s="168">
+      <c r="B29" s="166">
         <v>2</v>
       </c>
-      <c r="C29" s="164"/>
-      <c r="D29" s="48"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="47"/>
       <c r="E29" s="27"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
@@ -44664,11 +44684,11 @@
     </row>
     <row r="30" spans="1:24" ht="45.75" customHeight="1">
       <c r="A30" s="27"/>
-      <c r="B30" s="168">
+      <c r="B30" s="166">
         <v>3</v>
       </c>
-      <c r="C30" s="164"/>
-      <c r="D30" s="48"/>
+      <c r="C30" s="162"/>
+      <c r="D30" s="47"/>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
@@ -44692,11 +44712,11 @@
     </row>
     <row r="31" spans="1:24" ht="12.75" customHeight="1">
       <c r="A31" s="27"/>
-      <c r="B31" s="168">
+      <c r="B31" s="166">
         <v>4</v>
       </c>
-      <c r="C31" s="164"/>
-      <c r="D31" s="48"/>
+      <c r="C31" s="162"/>
+      <c r="D31" s="47"/>
       <c r="E31" s="27"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
@@ -44720,9 +44740,9 @@
     </row>
     <row r="32" spans="1:24" ht="12.75" customHeight="1">
       <c r="A32" s="27"/>
-      <c r="B32" s="169"/>
-      <c r="C32" s="170"/>
-      <c r="D32" s="171"/>
+      <c r="B32" s="167"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
@@ -44746,11 +44766,11 @@
     </row>
     <row r="33" spans="1:24" ht="12.75" customHeight="1">
       <c r="A33" s="27"/>
-      <c r="B33" s="172" t="s">
+      <c r="B33" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="172"/>
-      <c r="D33" s="162"/>
+      <c r="C33" s="170"/>
+      <c r="D33" s="160"/>
       <c r="E33" s="27"/>
       <c r="F33" s="27"/>
       <c r="G33" s="27"/>
@@ -44774,11 +44794,11 @@
     </row>
     <row r="34" spans="1:24" ht="12.75" customHeight="1">
       <c r="A34" s="27"/>
-      <c r="B34" s="168">
+      <c r="B34" s="166">
         <v>4</v>
       </c>
-      <c r="C34" s="113"/>
-      <c r="D34" s="48"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="47"/>
       <c r="E34" s="27"/>
       <c r="F34" s="27"/>
       <c r="G34" s="27"/>
@@ -44802,11 +44822,11 @@
     </row>
     <row r="35" spans="1:24" ht="12.75" customHeight="1">
       <c r="A35" s="27"/>
-      <c r="B35" s="168">
+      <c r="B35" s="166">
         <v>5</v>
       </c>
-      <c r="C35" s="113"/>
-      <c r="D35" s="48"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="47"/>
       <c r="E35" s="27"/>
       <c r="F35" s="27"/>
       <c r="G35" s="27"/>
@@ -44830,11 +44850,11 @@
     </row>
     <row r="36" spans="1:24" ht="12.75" customHeight="1">
       <c r="A36" s="27"/>
-      <c r="B36" s="168">
+      <c r="B36" s="166">
         <v>6</v>
       </c>
-      <c r="C36" s="113"/>
-      <c r="D36" s="48"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="47"/>
       <c r="E36" s="27"/>
       <c r="F36" s="27"/>
       <c r="G36" s="27"/>
@@ -44858,11 +44878,11 @@
     </row>
     <row r="37" spans="1:24" ht="12.75" customHeight="1">
       <c r="A37" s="27"/>
-      <c r="B37" s="168">
+      <c r="B37" s="166">
         <v>7</v>
       </c>
-      <c r="C37" s="113"/>
-      <c r="D37" s="48"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="47"/>
       <c r="E37" s="27"/>
       <c r="F37" s="27"/>
       <c r="G37" s="27"/>
@@ -44886,11 +44906,11 @@
     </row>
     <row r="38" spans="1:24" ht="12.75" customHeight="1">
       <c r="A38" s="27"/>
-      <c r="B38" s="168">
+      <c r="B38" s="166">
         <v>8</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="48"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="47"/>
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
       <c r="G38" s="27"/>
@@ -44914,11 +44934,11 @@
     </row>
     <row r="39" spans="1:24" ht="12.75" customHeight="1">
       <c r="A39" s="27"/>
-      <c r="B39" s="168">
+      <c r="B39" s="166">
         <v>9</v>
       </c>
-      <c r="C39" s="113"/>
-      <c r="D39" s="48"/>
+      <c r="C39" s="111"/>
+      <c r="D39" s="47"/>
       <c r="E39" s="27"/>
       <c r="F39" s="27"/>
       <c r="G39" s="27"/>
@@ -44942,11 +44962,11 @@
     </row>
     <row r="40" spans="1:24" ht="12.75" customHeight="1">
       <c r="A40" s="27"/>
-      <c r="B40" s="168">
+      <c r="B40" s="166">
         <v>10</v>
       </c>
-      <c r="C40" s="113"/>
-      <c r="D40" s="48"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="47"/>
       <c r="E40" s="27"/>
       <c r="F40" s="27"/>
       <c r="G40" s="27"/>
@@ -44970,10 +44990,10 @@
     </row>
     <row r="41" spans="1:24" ht="12.75" customHeight="1">
       <c r="A41" s="27"/>
-      <c r="B41" s="168">
+      <c r="B41" s="166">
         <v>11</v>
       </c>
-      <c r="C41" s="113"/>
+      <c r="C41" s="111"/>
       <c r="D41" s="33"/>
       <c r="E41" s="27"/>
       <c r="F41" s="27"/>
@@ -44998,11 +45018,11 @@
     </row>
     <row r="42" spans="1:24" ht="12.75" customHeight="1">
       <c r="A42" s="27"/>
-      <c r="B42" s="168">
+      <c r="B42" s="166">
         <v>12</v>
       </c>
-      <c r="C42" s="113"/>
-      <c r="D42" s="48"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="47"/>
       <c r="E42" s="27"/>
       <c r="F42" s="27"/>
       <c r="G42" s="27"/>
@@ -45026,11 +45046,11 @@
     </row>
     <row r="43" spans="1:24" ht="12.75" customHeight="1">
       <c r="A43" s="27"/>
-      <c r="B43" s="168">
+      <c r="B43" s="166">
         <v>13</v>
       </c>
-      <c r="C43" s="113"/>
-      <c r="D43" s="173"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="171"/>
       <c r="E43" s="27"/>
       <c r="F43" s="27"/>
       <c r="G43" s="27"/>
@@ -45054,11 +45074,11 @@
     </row>
     <row r="44" spans="1:24" ht="12.75" customHeight="1">
       <c r="A44" s="27"/>
-      <c r="B44" s="168">
+      <c r="B44" s="166">
         <v>14</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="48"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="47"/>
       <c r="E44" s="27"/>
       <c r="F44" s="27"/>
       <c r="G44" s="27"/>
@@ -45082,9 +45102,9 @@
     </row>
     <row r="45" spans="1:24" ht="12.75" customHeight="1">
       <c r="A45" s="27"/>
-      <c r="B45" s="174"/>
-      <c r="C45" s="175"/>
-      <c r="D45" s="171"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="173"/>
+      <c r="D45" s="169"/>
       <c r="E45" s="27"/>
       <c r="F45" s="27"/>
       <c r="G45" s="27"/>
@@ -45135,7 +45155,7 @@
     <row r="47" spans="1:24" ht="12.75" customHeight="1">
       <c r="A47" s="27"/>
       <c r="B47" s="27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -45166,7 +45186,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="27"/>
@@ -45196,7 +45216,7 @@
         <v>2</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="27"/>
@@ -45225,8 +45245,8 @@
       <c r="B50" s="27">
         <v>3</v>
       </c>
-      <c r="C50" s="113" t="s">
-        <v>174</v>
+      <c r="C50" s="111" t="s">
+        <v>172</v>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="27"/>
@@ -45256,7 +45276,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="27"/>
@@ -45286,7 +45306,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D52" s="27"/>
       <c r="E52" s="27"/>
